--- a/Cricket_Auction_Tracker.xlsx
+++ b/Cricket_Auction_Tracker.xlsx
@@ -9,21 +9,21 @@
   <sheets>
     <sheet name="Auction" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Balance" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Team 1" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Team 2" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Team 3" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Team 4" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Team 5" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Team 6" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Team 7" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Team 8" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Team 9" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Team 10" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Team 11" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Team 12" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Team 13" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Team 14" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Team 15" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Mumbai Indians" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Royal Challangers Banglore" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Chennai Super Kings" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Kolkata Knight Riders" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Patna Panthers" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Sunrisers Hydrabad" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Delhi Capitals" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Gujarat Titans" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Lucknow Super Giants" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Imphal Igniter" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Punjab Kings" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Rising Pune Super Giants" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Rajasthan Royals" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Kochi Tuskers" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Guwahati Chargers" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -613,15 +613,15 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Player_X</t>
+          <t>Rohit Sharma</t>
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>2</v>
+        <v>26.5</v>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>Team 4</t>
+          <t>Mumbai Indians</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -637,547 +637,1517 @@
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>Rohit S.</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="B6" s="10" t="n">
-        <v>3.5</v>
+        <v>12</v>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Team 1</t>
+          <t>Mumbai Indians</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Bumrah</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>4.2</v>
+        <v>20</v>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Team 4</t>
+          <t>Mumbai Indians</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>Kohli</t>
+          <t>Hugh Weibgen</t>
         </is>
       </c>
       <c r="B8" s="10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Team 7</t>
+          <t>Mumbai Indians</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Jadeja</t>
+          <t>Matthew Potts</t>
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>1.2</v>
+        <v>5</v>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>Team 1</t>
+          <t>Mumbai Indians</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="n"/>
-      <c r="B10" s="10" t="n"/>
-      <c r="C10" s="11" t="n"/>
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>Chamika Karunaratne</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>Mumbai Indians</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n"/>
-      <c r="B11" s="6" t="n"/>
-      <c r="C11" s="7" t="n"/>
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Karun Nair</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Mumbai Indians</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="n"/>
-      <c r="B12" s="10" t="n"/>
-      <c r="C12" s="11" t="n"/>
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>Sachin Baby</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>Mumbai Indians</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n"/>
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" s="7" t="n"/>
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Anrich Nortje</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Mumbai Indians</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="n"/>
-      <c r="B14" s="10" t="n"/>
-      <c r="C14" s="11" t="n"/>
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>Navdeep Saini</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>Royal Challangers Banglore</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n"/>
-      <c r="B15" s="6" t="n"/>
-      <c r="C15" s="7" t="n"/>
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Harnoor Singh</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Royal Challangers Banglore</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="n"/>
-      <c r="B16" s="10" t="n"/>
-      <c r="C16" s="11" t="n"/>
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>Swastik Chikara</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>Royal Challangers Banglore</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n"/>
-      <c r="B17" s="6" t="n"/>
-      <c r="C17" s="7" t="n"/>
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Tilak Varma</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Royal Challangers Banglore</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="n"/>
-      <c r="B18" s="10" t="n"/>
-      <c r="C18" s="11" t="n"/>
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>Dawid Malan</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>Royal Challangers Banglore</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n"/>
-      <c r="B19" s="6" t="n"/>
-      <c r="C19" s="7" t="n"/>
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Haris Rauf</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Royal Challangers Banglore</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="n"/>
-      <c r="B20" s="10" t="n"/>
-      <c r="C20" s="11" t="n"/>
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>George Scrimshaw</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>Royal Challangers Banglore</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n"/>
-      <c r="B21" s="6" t="n"/>
-      <c r="C21" s="7" t="n"/>
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Hasan Ali</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>Royal Challangers Banglore</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="n"/>
-      <c r="B22" s="10" t="n"/>
-      <c r="C22" s="11" t="n"/>
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>Usma Mir</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>Royal Challangers Banglore</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n"/>
-      <c r="B23" s="6" t="n"/>
-      <c r="C23" s="7" t="n"/>
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Jimmy Neesham</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>Royal Challangers Banglore</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="n"/>
-      <c r="B24" s="10" t="n"/>
-      <c r="C24" s="11" t="n"/>
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>Parth Rekhade</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>Royal Challangers Banglore</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n"/>
-      <c r="B25" s="6" t="n"/>
-      <c r="C25" s="7" t="n"/>
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Dinesh Bana</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>Royal Challangers Banglore</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="n"/>
-      <c r="B26" s="10" t="n"/>
-      <c r="C26" s="11" t="n"/>
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>Yuzvendra Chahal</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>Royal Challangers Banglore</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n"/>
-      <c r="B27" s="6" t="n"/>
-      <c r="C27" s="7" t="n"/>
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Sandeep Sharma</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>Chennai Super Kings</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="n"/>
-      <c r="B28" s="10" t="n"/>
-      <c r="C28" s="11" t="n"/>
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>Sarafaz Khan</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>Chennai Super Kings</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n"/>
-      <c r="B29" s="6" t="n"/>
-      <c r="C29" s="7" t="n"/>
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Arjun Tendulkar</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>Chennai Super Kings</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="n"/>
-      <c r="B30" s="10" t="n"/>
-      <c r="C30" s="11" t="n"/>
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>Ruturaj Gaikwad</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>Chennai Super Kings</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n"/>
-      <c r="B31" s="6" t="n"/>
-      <c r="C31" s="7" t="n"/>
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Romario Shepherd</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>Chennai Super Kings</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="n"/>
-      <c r="B32" s="10" t="n"/>
-      <c r="C32" s="11" t="n"/>
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>Tom Latham</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>Chennai Super Kings</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n"/>
-      <c r="B33" s="6" t="n"/>
-      <c r="C33" s="7" t="n"/>
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Shaheen Shah Afridi</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>Chennai Super Kings</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="9" t="n"/>
-      <c r="B34" s="10" t="n"/>
-      <c r="C34" s="11" t="n"/>
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>Naseem Shah</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t>Chennai Super Kings</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n"/>
-      <c r="B35" s="6" t="n"/>
-      <c r="C35" s="7" t="n"/>
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Mohammad Amir</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>Chennai Super Kings</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="9" t="n"/>
-      <c r="B36" s="10" t="n"/>
-      <c r="C36" s="11" t="n"/>
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>Akhil</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>Chennai Super Kings</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n"/>
-      <c r="B37" s="6" t="n"/>
-      <c r="C37" s="7" t="n"/>
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>Devdutt Padikkal</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>Kolkata Knight Riders</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="9" t="n"/>
-      <c r="B38" s="10" t="n"/>
-      <c r="C38" s="11" t="n"/>
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>Vaibhav Suryavanshi</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>Kolkata Knight Riders</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n"/>
-      <c r="B39" s="6" t="n"/>
-      <c r="C39" s="7" t="n"/>
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>Sikandar Raza</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>Kolkata Knight Riders</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="9" t="n"/>
-      <c r="B40" s="10" t="n"/>
-      <c r="C40" s="11" t="n"/>
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>Ashutosh Sharma</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="C40" s="11" t="inlineStr">
+        <is>
+          <t>Kolkata Knight Riders</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n"/>
-      <c r="B41" s="6" t="n"/>
-      <c r="C41" s="7" t="n"/>
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>Dharmendrasinh Jadeja</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>Kolkata Knight Riders</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="9" t="n"/>
-      <c r="B42" s="10" t="n"/>
-      <c r="C42" s="11" t="n"/>
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>Sameer Rizvi</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="C42" s="11" t="inlineStr">
+        <is>
+          <t>Kolkata Knight Riders</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="n"/>
-      <c r="B43" s="6" t="n"/>
-      <c r="C43" s="7" t="n"/>
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>T. Natarajan</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>Kolkata Knight Riders</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="9" t="n"/>
-      <c r="B44" s="10" t="n"/>
-      <c r="C44" s="11" t="n"/>
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>Umesh Yadav</t>
+        </is>
+      </c>
+      <c r="B44" s="10" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="C44" s="11" t="inlineStr">
+        <is>
+          <t>Patna Panthers</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="n"/>
-      <c r="B45" s="6" t="n"/>
-      <c r="C45" s="7" t="n"/>
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>Liam Livingstone</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>Patna Panthers</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="9" t="n"/>
-      <c r="B46" s="10" t="n"/>
-      <c r="C46" s="11" t="n"/>
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>Rahul Tripathi</t>
+        </is>
+      </c>
+      <c r="B46" s="10" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="C46" s="11" t="inlineStr">
+        <is>
+          <t>Patna Panthers</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="n"/>
-      <c r="B47" s="6" t="n"/>
-      <c r="C47" s="7" t="n"/>
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>Suryakumar Yadav</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>Patna Panthers</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="9" t="n"/>
-      <c r="B48" s="10" t="n"/>
-      <c r="C48" s="11" t="n"/>
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t>Tim Seifert</t>
+        </is>
+      </c>
+      <c r="B48" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="C48" s="11" t="inlineStr">
+        <is>
+          <t>Patna Panthers</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="n"/>
-      <c r="B49" s="6" t="n"/>
-      <c r="C49" s="7" t="n"/>
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>Spencer Johnson</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>Patna Panthers</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" s="9" t="n"/>
-      <c r="B50" s="10" t="n"/>
-      <c r="C50" s="11" t="n"/>
+      <c r="A50" s="9" t="inlineStr">
+        <is>
+          <t>Lhuan-dré Pretorius</t>
+        </is>
+      </c>
+      <c r="B50" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="C50" s="11" t="inlineStr">
+        <is>
+          <t>Sunrisers Hydrabad</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="n"/>
-      <c r="B51" s="6" t="n"/>
-      <c r="C51" s="7" t="n"/>
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>KL Rahul</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>Sunrisers Hydrabad</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="9" t="n"/>
-      <c r="B52" s="10" t="n"/>
-      <c r="C52" s="11" t="n"/>
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>Angkrish Raghuvanshi</t>
+        </is>
+      </c>
+      <c r="B52" s="10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="C52" s="11" t="inlineStr">
+        <is>
+          <t>Sunrisers Hydrabad</t>
+        </is>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="n"/>
-      <c r="B53" s="6" t="n"/>
-      <c r="C53" s="7" t="n"/>
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>Mohammed Siraj</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>Sunrisers Hydrabad</t>
+        </is>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" s="9" t="n"/>
-      <c r="B54" s="10" t="n"/>
-      <c r="C54" s="11" t="n"/>
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>Baba Indrajith</t>
+        </is>
+      </c>
+      <c r="B54" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C54" s="11" t="inlineStr">
+        <is>
+          <t>Sunrisers Hydrabad</t>
+        </is>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="n"/>
-      <c r="B55" s="6" t="n"/>
-      <c r="C55" s="7" t="n"/>
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>Nitish Rana</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>Delhi Capitals</t>
+        </is>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" s="9" t="n"/>
-      <c r="B56" s="10" t="n"/>
-      <c r="C56" s="11" t="n"/>
+      <c r="A56" s="9" t="inlineStr">
+        <is>
+          <t>Ben McKinney</t>
+        </is>
+      </c>
+      <c r="B56" s="10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C56" s="11" t="inlineStr">
+        <is>
+          <t>Delhi Capitals</t>
+        </is>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="n"/>
-      <c r="B57" s="6" t="n"/>
-      <c r="C57" s="7" t="n"/>
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>Keshav Maharaj</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>Delhi Capitals</t>
+        </is>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" s="9" t="n"/>
-      <c r="B58" s="10" t="n"/>
-      <c r="C58" s="11" t="n"/>
+      <c r="A58" s="9" t="inlineStr">
+        <is>
+          <t>Abrar Ahmed</t>
+        </is>
+      </c>
+      <c r="B58" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="C58" s="11" t="inlineStr">
+        <is>
+          <t>Delhi Capitals</t>
+        </is>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="n"/>
-      <c r="B59" s="6" t="n"/>
-      <c r="C59" s="7" t="n"/>
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>Faf Du Plesis</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>Delhi Capitals</t>
+        </is>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" s="9" t="n"/>
-      <c r="B60" s="10" t="n"/>
-      <c r="C60" s="11" t="n"/>
+      <c r="A60" s="9" t="inlineStr">
+        <is>
+          <t>Rajat Patidar</t>
+        </is>
+      </c>
+      <c r="B60" s="10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="C60" s="11" t="inlineStr">
+        <is>
+          <t>Delhi Capitals</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="n"/>
-      <c r="B61" s="6" t="n"/>
-      <c r="C61" s="7" t="n"/>
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>Rinku Singh</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>Gujarat Titans</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" s="9" t="n"/>
-      <c r="B62" s="10" t="n"/>
-      <c r="C62" s="11" t="n"/>
+      <c r="A62" s="9" t="inlineStr">
+        <is>
+          <t>Sai Sudharsan</t>
+        </is>
+      </c>
+      <c r="B62" s="10" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="C62" s="11" t="inlineStr">
+        <is>
+          <t>Gujarat Titans</t>
+        </is>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="n"/>
-      <c r="B63" s="6" t="n"/>
-      <c r="C63" s="7" t="n"/>
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>Ishaan Kishaan</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>Gujarat Titans</t>
+        </is>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" s="9" t="n"/>
-      <c r="B64" s="10" t="n"/>
-      <c r="C64" s="11" t="n"/>
+      <c r="A64" s="9" t="inlineStr">
+        <is>
+          <t>Govinda Poddar</t>
+        </is>
+      </c>
+      <c r="B64" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C64" s="11" t="inlineStr">
+        <is>
+          <t>Gujarat Titans</t>
+        </is>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="n"/>
-      <c r="B65" s="6" t="n"/>
-      <c r="C65" s="7" t="n"/>
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>Sanju Samson</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t>Lucknow Super Giants</t>
+        </is>
+      </c>
     </row>
     <row r="66">
-      <c r="A66" s="9" t="n"/>
-      <c r="B66" s="10" t="n"/>
-      <c r="C66" s="11" t="n"/>
+      <c r="A66" s="9" t="inlineStr">
+        <is>
+          <t>Dewald Brevis</t>
+        </is>
+      </c>
+      <c r="B66" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="C66" s="11" t="inlineStr">
+        <is>
+          <t>Lucknow Super Giants</t>
+        </is>
+      </c>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="n"/>
-      <c r="B67" s="6" t="n"/>
-      <c r="C67" s="7" t="n"/>
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>Mayank Dagar</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C67" s="7" t="inlineStr">
+        <is>
+          <t>Lucknow Super Giants</t>
+        </is>
+      </c>
     </row>
     <row r="68">
-      <c r="A68" s="9" t="n"/>
-      <c r="B68" s="10" t="n"/>
-      <c r="C68" s="11" t="n"/>
+      <c r="A68" s="9" t="inlineStr">
+        <is>
+          <t>Abhishek Sharma</t>
+        </is>
+      </c>
+      <c r="B68" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="C68" s="11" t="inlineStr">
+        <is>
+          <t>Lucknow Super Giants</t>
+        </is>
+      </c>
     </row>
     <row r="69">
-      <c r="A69" s="5" t="n"/>
-      <c r="B69" s="6" t="n"/>
-      <c r="C69" s="7" t="n"/>
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>Shaik Rasheed</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C69" s="7" t="inlineStr">
+        <is>
+          <t>Imphal Igniter</t>
+        </is>
+      </c>
     </row>
     <row r="70">
-      <c r="A70" s="9" t="n"/>
-      <c r="B70" s="10" t="n"/>
-      <c r="C70" s="11" t="n"/>
+      <c r="A70" s="9" t="inlineStr">
+        <is>
+          <t>Chetan Sakariya</t>
+        </is>
+      </c>
+      <c r="B70" s="10" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="C70" s="11" t="inlineStr">
+        <is>
+          <t>Imphal Igniter</t>
+        </is>
+      </c>
     </row>
     <row r="71">
-      <c r="A71" s="5" t="n"/>
-      <c r="B71" s="6" t="n"/>
-      <c r="C71" s="7" t="n"/>
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>Quinton de Kock</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="C71" s="7" t="inlineStr">
+        <is>
+          <t>Imphal Igniter</t>
+        </is>
+      </c>
     </row>
     <row r="72">
-      <c r="A72" s="9" t="n"/>
-      <c r="B72" s="10" t="n"/>
-      <c r="C72" s="11" t="n"/>
+      <c r="A72" s="9" t="inlineStr">
+        <is>
+          <t>Joe Root</t>
+        </is>
+      </c>
+      <c r="B72" s="10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C72" s="11" t="inlineStr">
+        <is>
+          <t>Imphal Igniter</t>
+        </is>
+      </c>
     </row>
     <row r="73">
-      <c r="A73" s="5" t="n"/>
-      <c r="B73" s="6" t="n"/>
-      <c r="C73" s="7" t="n"/>
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>Virat Kohli</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t>Imphal Igniter</t>
+        </is>
+      </c>
     </row>
     <row r="74">
-      <c r="A74" s="9" t="n"/>
-      <c r="B74" s="10" t="n"/>
-      <c r="C74" s="11" t="n"/>
+      <c r="A74" s="9" t="inlineStr">
+        <is>
+          <t>Vidwath Kaverappa</t>
+        </is>
+      </c>
+      <c r="B74" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C74" s="11" t="inlineStr">
+        <is>
+          <t>Imphal Igniter</t>
+        </is>
+      </c>
     </row>
     <row r="75">
-      <c r="A75" s="5" t="n"/>
-      <c r="B75" s="6" t="n"/>
-      <c r="C75" s="7" t="n"/>
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>Siddharth Desai</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C75" s="7" t="inlineStr">
+        <is>
+          <t>Imphal Igniter</t>
+        </is>
+      </c>
     </row>
     <row r="76">
-      <c r="A76" s="9" t="n"/>
-      <c r="B76" s="10" t="n"/>
-      <c r="C76" s="11" t="n"/>
+      <c r="A76" s="9" t="inlineStr">
+        <is>
+          <t>Ishant Sharma</t>
+        </is>
+      </c>
+      <c r="B76" s="10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C76" s="11" t="inlineStr">
+        <is>
+          <t>Punjab Kings</t>
+        </is>
+      </c>
     </row>
     <row r="77">
-      <c r="A77" s="5" t="n"/>
-      <c r="B77" s="6" t="n"/>
-      <c r="C77" s="7" t="n"/>
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>Deepak Hooda</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C77" s="7" t="inlineStr">
+        <is>
+          <t>Punjab Kings</t>
+        </is>
+      </c>
     </row>
     <row r="78">
-      <c r="A78" s="9" t="n"/>
-      <c r="B78" s="10" t="n"/>
-      <c r="C78" s="11" t="n"/>
+      <c r="A78" s="9" t="inlineStr">
+        <is>
+          <t>Sam Konstas</t>
+        </is>
+      </c>
+      <c r="B78" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="C78" s="11" t="inlineStr">
+        <is>
+          <t>Punjab Kings</t>
+        </is>
+      </c>
     </row>
     <row r="79">
-      <c r="A79" s="5" t="n"/>
-      <c r="B79" s="6" t="n"/>
-      <c r="C79" s="7" t="n"/>
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>Jitesh Sharma</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="C79" s="7" t="inlineStr">
+        <is>
+          <t>Punjab Kings</t>
+        </is>
+      </c>
     </row>
     <row r="80">
-      <c r="A80" s="9" t="n"/>
-      <c r="B80" s="10" t="n"/>
-      <c r="C80" s="11" t="n"/>
+      <c r="A80" s="9" t="inlineStr">
+        <is>
+          <t>Shubman Gill</t>
+        </is>
+      </c>
+      <c r="B80" s="10" t="n">
+        <v>28</v>
+      </c>
+      <c r="C80" s="11" t="inlineStr">
+        <is>
+          <t>Punjab Kings</t>
+        </is>
+      </c>
     </row>
     <row r="81">
-      <c r="A81" s="5" t="n"/>
-      <c r="B81" s="6" t="n"/>
-      <c r="C81" s="7" t="n"/>
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>Mitchell Starc</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="C81" s="7" t="inlineStr">
+        <is>
+          <t>Punjab Kings</t>
+        </is>
+      </c>
     </row>
     <row r="82">
-      <c r="A82" s="9" t="n"/>
-      <c r="B82" s="10" t="n"/>
-      <c r="C82" s="11" t="n"/>
+      <c r="A82" s="9" t="inlineStr">
+        <is>
+          <t>Jasprit Bumrah</t>
+        </is>
+      </c>
+      <c r="B82" s="10" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="C82" s="11" t="inlineStr">
+        <is>
+          <t>Rising Pune Super Giants</t>
+        </is>
+      </c>
     </row>
     <row r="83">
-      <c r="A83" s="5" t="n"/>
-      <c r="B83" s="6" t="n"/>
-      <c r="C83" s="7" t="n"/>
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>Moeen Ali</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="C83" s="7" t="inlineStr">
+        <is>
+          <t>Rising Pune Super Giants</t>
+        </is>
+      </c>
     </row>
     <row r="84">
-      <c r="A84" s="9" t="n"/>
-      <c r="B84" s="10" t="n"/>
-      <c r="C84" s="11" t="n"/>
+      <c r="A84" s="9" t="inlineStr">
+        <is>
+          <t>Will Jacks</t>
+        </is>
+      </c>
+      <c r="B84" s="10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="C84" s="11" t="inlineStr">
+        <is>
+          <t>Rising Pune Super Giants</t>
+        </is>
+      </c>
     </row>
     <row r="85">
-      <c r="A85" s="5" t="n"/>
-      <c r="B85" s="6" t="n"/>
-      <c r="C85" s="7" t="n"/>
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>Dasun Shanaka</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="C85" s="7" t="inlineStr">
+        <is>
+          <t>Rising Pune Super Giants</t>
+        </is>
+      </c>
     </row>
     <row r="86">
-      <c r="A86" s="9" t="n"/>
-      <c r="B86" s="10" t="n"/>
-      <c r="C86" s="11" t="n"/>
+      <c r="A86" s="9" t="inlineStr">
+        <is>
+          <t>Amit Shukla</t>
+        </is>
+      </c>
+      <c r="B86" s="10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C86" s="11" t="inlineStr">
+        <is>
+          <t>Rising Pune Super Giants</t>
+        </is>
+      </c>
     </row>
     <row r="87">
-      <c r="A87" s="5" t="n"/>
-      <c r="B87" s="6" t="n"/>
-      <c r="C87" s="7" t="n"/>
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>Abhishek Powel</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="C87" s="7" t="inlineStr">
+        <is>
+          <t>Rising Pune Super Giants</t>
+        </is>
+      </c>
     </row>
     <row r="88">
-      <c r="A88" s="9" t="n"/>
-      <c r="B88" s="10" t="n"/>
-      <c r="C88" s="11" t="n"/>
+      <c r="A88" s="9" t="inlineStr">
+        <is>
+          <t>Harpreet Bhatia</t>
+        </is>
+      </c>
+      <c r="B88" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C88" s="11" t="inlineStr">
+        <is>
+          <t>Rajasthan Royals</t>
+        </is>
+      </c>
     </row>
     <row r="89">
-      <c r="A89" s="5" t="n"/>
-      <c r="B89" s="6" t="n"/>
-      <c r="C89" s="7" t="n"/>
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>Musheer Khan</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C89" s="7" t="inlineStr">
+        <is>
+          <t>Rajasthan Royals</t>
+        </is>
+      </c>
     </row>
     <row r="90">
-      <c r="A90" s="9" t="n"/>
-      <c r="B90" s="10" t="n"/>
-      <c r="C90" s="11" t="n"/>
+      <c r="A90" s="9" t="inlineStr">
+        <is>
+          <t>Avesh Khan</t>
+        </is>
+      </c>
+      <c r="B90" s="10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="C90" s="11" t="inlineStr">
+        <is>
+          <t>Rajasthan Royals</t>
+        </is>
+      </c>
     </row>
     <row r="91">
-      <c r="A91" s="5" t="n"/>
-      <c r="B91" s="6" t="n"/>
-      <c r="C91" s="7" t="n"/>
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>MS Dhoni</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="C91" s="7" t="inlineStr">
+        <is>
+          <t>Rajasthan Royals</t>
+        </is>
+      </c>
     </row>
     <row r="92">
-      <c r="A92" s="9" t="n"/>
-      <c r="B92" s="10" t="n"/>
-      <c r="C92" s="11" t="n"/>
+      <c r="A92" s="9" t="inlineStr">
+        <is>
+          <t>Glenn Maxwell</t>
+        </is>
+      </c>
+      <c r="B92" s="10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="C92" s="11" t="inlineStr">
+        <is>
+          <t>Rajasthan Royals</t>
+        </is>
+      </c>
     </row>
     <row r="93">
-      <c r="A93" s="5" t="n"/>
-      <c r="B93" s="6" t="n"/>
-      <c r="C93" s="7" t="n"/>
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>Tom Bruce</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C93" s="7" t="inlineStr">
+        <is>
+          <t>Rajasthan Royals</t>
+        </is>
+      </c>
     </row>
     <row r="94">
-      <c r="A94" s="9" t="n"/>
-      <c r="B94" s="10" t="n"/>
-      <c r="C94" s="11" t="n"/>
+      <c r="A94" s="9" t="inlineStr">
+        <is>
+          <t>Harry Dixon</t>
+        </is>
+      </c>
+      <c r="B94" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C94" s="11" t="inlineStr">
+        <is>
+          <t>Rajasthan Royals</t>
+        </is>
+      </c>
     </row>
     <row r="95">
-      <c r="A95" s="5" t="n"/>
-      <c r="B95" s="6" t="n"/>
-      <c r="C95" s="7" t="n"/>
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>Ajinkya Rahane</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="C95" s="7" t="inlineStr">
+        <is>
+          <t>Rajasthan Royals</t>
+        </is>
+      </c>
     </row>
     <row r="96">
-      <c r="A96" s="9" t="n"/>
-      <c r="B96" s="10" t="n"/>
-      <c r="C96" s="11" t="n"/>
+      <c r="A96" s="9" t="inlineStr">
+        <is>
+          <t>Priyansh Arya</t>
+        </is>
+      </c>
+      <c r="B96" s="10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="C96" s="11" t="inlineStr">
+        <is>
+          <t>Rajasthan Royals</t>
+        </is>
+      </c>
     </row>
     <row r="97">
-      <c r="A97" s="5" t="n"/>
-      <c r="B97" s="6" t="n"/>
-      <c r="C97" s="7" t="n"/>
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>Jason Holder</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="C97" s="7" t="inlineStr">
+        <is>
+          <t>Kochi Tuskers</t>
+        </is>
+      </c>
     </row>
     <row r="98">
-      <c r="A98" s="9" t="n"/>
-      <c r="B98" s="10" t="n"/>
-      <c r="C98" s="11" t="n"/>
+      <c r="A98" s="9" t="inlineStr">
+        <is>
+          <t>Kagiso Rabada</t>
+        </is>
+      </c>
+      <c r="B98" s="10" t="n">
+        <v>22</v>
+      </c>
+      <c r="C98" s="11" t="inlineStr">
+        <is>
+          <t>Kochi Tuskers</t>
+        </is>
+      </c>
     </row>
     <row r="99">
-      <c r="A99" s="5" t="n"/>
-      <c r="B99" s="6" t="n"/>
-      <c r="C99" s="7" t="n"/>
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>Heinrich Klassen</t>
+        </is>
+      </c>
+      <c r="B99" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="C99" s="7" t="inlineStr">
+        <is>
+          <t>Kochi Tuskers</t>
+        </is>
+      </c>
     </row>
     <row r="100">
-      <c r="A100" s="9" t="n"/>
-      <c r="B100" s="10" t="n"/>
-      <c r="C100" s="11" t="n"/>
+      <c r="A100" s="9" t="inlineStr">
+        <is>
+          <t>Nikhil Gangta</t>
+        </is>
+      </c>
+      <c r="B100" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C100" s="11" t="inlineStr">
+        <is>
+          <t>Kochi Tuskers</t>
+        </is>
+      </c>
     </row>
     <row r="101">
-      <c r="A101" s="5" t="n"/>
-      <c r="B101" s="6" t="n"/>
-      <c r="C101" s="7" t="n"/>
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>Hardik Pandya</t>
+        </is>
+      </c>
+      <c r="B101" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="C101" s="7" t="inlineStr">
+        <is>
+          <t>Guwahati Chargers</t>
+        </is>
+      </c>
     </row>
     <row r="102">
-      <c r="A102" s="9" t="n"/>
-      <c r="B102" s="10" t="n"/>
-      <c r="C102" s="11" t="n"/>
+      <c r="A102" s="9" t="inlineStr">
+        <is>
+          <t>Shakib Al Hasan</t>
+        </is>
+      </c>
+      <c r="B102" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="C102" s="11" t="inlineStr">
+        <is>
+          <t>Guwahati Chargers</t>
+        </is>
+      </c>
     </row>
     <row r="103">
-      <c r="A103" s="5" t="n"/>
-      <c r="B103" s="6" t="n"/>
-      <c r="C103" s="7" t="n"/>
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>Nehal Wadhera</t>
+        </is>
+      </c>
+      <c r="B103" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C103" s="7" t="inlineStr">
+        <is>
+          <t>Guwahati Chargers</t>
+        </is>
+      </c>
     </row>
     <row r="104">
-      <c r="A104" s="9" t="n"/>
-      <c r="B104" s="10" t="n"/>
-      <c r="C104" s="11" t="n"/>
+      <c r="A104" s="9" t="inlineStr">
+        <is>
+          <t>Rishabh Pant</t>
+        </is>
+      </c>
+      <c r="B104" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="C104" s="11" t="inlineStr">
+        <is>
+          <t>Guwahati Chargers</t>
+        </is>
+      </c>
     </row>
     <row r="105">
-      <c r="A105" s="5" t="n"/>
-      <c r="B105" s="6" t="n"/>
-      <c r="C105" s="7" t="n"/>
+      <c r="A105" s="5" t="inlineStr">
+        <is>
+          <t>Wiaan Mulder</t>
+        </is>
+      </c>
+      <c r="B105" s="6" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="C105" s="7" t="inlineStr">
+        <is>
+          <t>Guwahati Chargers</t>
+        </is>
+      </c>
     </row>
     <row r="106">
-      <c r="A106" s="9" t="n"/>
-      <c r="B106" s="10" t="n"/>
-      <c r="C106" s="11" t="n"/>
+      <c r="A106" s="9" t="inlineStr">
+        <is>
+          <t>Maheesh Theekshana</t>
+        </is>
+      </c>
+      <c r="B106" s="10" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="C106" s="11" t="inlineStr">
+        <is>
+          <t>Guwahati Chargers</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="n"/>
@@ -9596,7 +10566,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Team 1</t>
+          <t>Mumbai Indians</t>
         </is>
       </c>
       <c r="B4" s="6" t="n">
@@ -9618,7 +10588,7 @@
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>Team 2</t>
+          <t>Royal Challangers Banglore</t>
         </is>
       </c>
       <c r="B5" s="10" t="n">
@@ -9640,7 +10610,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Team 3</t>
+          <t>Chennai Super Kings</t>
         </is>
       </c>
       <c r="B6" s="6" t="n">
@@ -9662,7 +10632,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>Team 4</t>
+          <t>Kolkata Knight Riders</t>
         </is>
       </c>
       <c r="B7" s="10" t="n">
@@ -9684,7 +10654,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Team 5</t>
+          <t>Patna Panthers</t>
         </is>
       </c>
       <c r="B8" s="6" t="n">
@@ -9706,7 +10676,7 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>Team 6</t>
+          <t>Sunrisers Hydrabad</t>
         </is>
       </c>
       <c r="B9" s="10" t="n">
@@ -9728,7 +10698,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Team 7</t>
+          <t>Delhi Capitals</t>
         </is>
       </c>
       <c r="B10" s="6" t="n">
@@ -9750,7 +10720,7 @@
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>Team 8</t>
+          <t>Gujarat Titans</t>
         </is>
       </c>
       <c r="B11" s="10" t="n">
@@ -9772,7 +10742,7 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Team 9</t>
+          <t>Lucknow Super Giants</t>
         </is>
       </c>
       <c r="B12" s="6" t="n">
@@ -9794,7 +10764,7 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>Team 10</t>
+          <t>Imphal Igniter</t>
         </is>
       </c>
       <c r="B13" s="10" t="n">
@@ -9816,7 +10786,7 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Team 11</t>
+          <t>Punjab Kings</t>
         </is>
       </c>
       <c r="B14" s="6" t="n">
@@ -9838,7 +10808,7 @@
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>Team 12</t>
+          <t>Rising Pune Super Giants</t>
         </is>
       </c>
       <c r="B15" s="10" t="n">
@@ -9860,7 +10830,7 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Team 13</t>
+          <t>Rajasthan Royals</t>
         </is>
       </c>
       <c r="B16" s="6" t="n">
@@ -9882,7 +10852,7 @@
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>Team 14</t>
+          <t>Kochi Tuskers</t>
         </is>
       </c>
       <c r="B17" s="10" t="n">
@@ -9904,7 +10874,7 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Team 15</t>
+          <t>Guwahati Chargers</t>
         </is>
       </c>
       <c r="B18" s="6" t="n">

--- a/Cricket_Auction_Tracker.xlsx
+++ b/Cricket_Auction_Tracker.xlsx
@@ -9,21 +9,22 @@
   <sheets>
     <sheet name="Auction" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Balance" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Mumbai Indians" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Royal Challangers Banglore" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Chennai Super Kings" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Kolkata Knight Riders" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Patna Panthers" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Sunrisers Hydrabad" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Delhi Capitals" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Gujarat Titans" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Lucknow Super Giants" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Imphal Igniter" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Punjab Kings" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Rising Pune Super Giants" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Rajasthan Royals" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Kochi Tuskers" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Guwahati Chargers" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Mumbai Indians" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Royal Challangers Banglore" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Chennai Super Kings" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Kolkata Knight Riders" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Patna Panthers" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Sunrisers Hydrabad" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Delhi Capitals" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Gujarat Titans" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Lucknow Super Giants" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Imphal Igniter" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Punjab Kings" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Rising Pune Super Giants" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Rajasthan Royals" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Kochi Tuskers" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Guwahati Chargers" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -33,7 +34,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -66,6 +67,11 @@
     <font>
       <b val="1"/>
       <color rgb="002E7D32"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="8">
@@ -132,7 +138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -172,6 +178,24 @@
     </xf>
     <xf numFmtId="1" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -6648,52 +6672,52 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="16">
-        <f>Balance!A11</f>
+      <c r="A1" s="22">
+        <f>Balance!A10</f>
         <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="17" t="inlineStr">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t>Purse (Cr)</t>
         </is>
       </c>
-      <c r="B3" s="18">
-        <f>Balance!B11</f>
+      <c r="B3" s="24">
+        <f>Balance!B10</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="23" t="inlineStr">
         <is>
           <t>Spent (Cr)</t>
         </is>
       </c>
-      <c r="B4" s="18">
-        <f>Balance!C11</f>
+      <c r="B4" s="24">
+        <f>Balance!C10</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Balance (Cr)</t>
         </is>
       </c>
-      <c r="B5" s="20">
-        <f>Balance!D11</f>
+      <c r="B5" s="26">
+        <f>Balance!D10</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="27" t="inlineStr">
         <is>
           <t>Players</t>
         </is>
       </c>
-      <c r="B6" s="22">
-        <f>Balance!E11</f>
+      <c r="B6" s="28">
+        <f>Balance!E10</f>
         <v/>
       </c>
     </row>
@@ -7132,52 +7156,52 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="16">
-        <f>Balance!A12</f>
+      <c r="A1" s="22">
+        <f>Balance!A11</f>
         <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="17" t="inlineStr">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t>Purse (Cr)</t>
         </is>
       </c>
-      <c r="B3" s="18">
-        <f>Balance!B12</f>
+      <c r="B3" s="24">
+        <f>Balance!B11</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="23" t="inlineStr">
         <is>
           <t>Spent (Cr)</t>
         </is>
       </c>
-      <c r="B4" s="18">
-        <f>Balance!C12</f>
+      <c r="B4" s="24">
+        <f>Balance!C11</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Balance (Cr)</t>
         </is>
       </c>
-      <c r="B5" s="20">
-        <f>Balance!D12</f>
+      <c r="B5" s="26">
+        <f>Balance!D11</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="27" t="inlineStr">
         <is>
           <t>Players</t>
         </is>
       </c>
-      <c r="B6" s="22">
-        <f>Balance!E12</f>
+      <c r="B6" s="28">
+        <f>Balance!E11</f>
         <v/>
       </c>
     </row>
@@ -7616,52 +7640,52 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="16">
-        <f>Balance!A13</f>
+      <c r="A1" s="22">
+        <f>Balance!A12</f>
         <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="17" t="inlineStr">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t>Purse (Cr)</t>
         </is>
       </c>
-      <c r="B3" s="18">
-        <f>Balance!B13</f>
+      <c r="B3" s="24">
+        <f>Balance!B12</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="23" t="inlineStr">
         <is>
           <t>Spent (Cr)</t>
         </is>
       </c>
-      <c r="B4" s="18">
-        <f>Balance!C13</f>
+      <c r="B4" s="24">
+        <f>Balance!C12</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Balance (Cr)</t>
         </is>
       </c>
-      <c r="B5" s="20">
-        <f>Balance!D13</f>
+      <c r="B5" s="26">
+        <f>Balance!D12</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="27" t="inlineStr">
         <is>
           <t>Players</t>
         </is>
       </c>
-      <c r="B6" s="22">
-        <f>Balance!E13</f>
+      <c r="B6" s="28">
+        <f>Balance!E12</f>
         <v/>
       </c>
     </row>
@@ -8100,52 +8124,52 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="16">
-        <f>Balance!A14</f>
+      <c r="A1" s="22">
+        <f>Balance!A13</f>
         <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="17" t="inlineStr">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t>Purse (Cr)</t>
         </is>
       </c>
-      <c r="B3" s="18">
-        <f>Balance!B14</f>
+      <c r="B3" s="24">
+        <f>Balance!B13</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="23" t="inlineStr">
         <is>
           <t>Spent (Cr)</t>
         </is>
       </c>
-      <c r="B4" s="18">
-        <f>Balance!C14</f>
+      <c r="B4" s="24">
+        <f>Balance!C13</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Balance (Cr)</t>
         </is>
       </c>
-      <c r="B5" s="20">
-        <f>Balance!D14</f>
+      <c r="B5" s="26">
+        <f>Balance!D13</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="27" t="inlineStr">
         <is>
           <t>Players</t>
         </is>
       </c>
-      <c r="B6" s="22">
-        <f>Balance!E14</f>
+      <c r="B6" s="28">
+        <f>Balance!E13</f>
         <v/>
       </c>
     </row>
@@ -8584,52 +8608,52 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="16">
-        <f>Balance!A15</f>
+      <c r="A1" s="22">
+        <f>Balance!A14</f>
         <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="17" t="inlineStr">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t>Purse (Cr)</t>
         </is>
       </c>
-      <c r="B3" s="18">
-        <f>Balance!B15</f>
+      <c r="B3" s="24">
+        <f>Balance!B14</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="23" t="inlineStr">
         <is>
           <t>Spent (Cr)</t>
         </is>
       </c>
-      <c r="B4" s="18">
-        <f>Balance!C15</f>
+      <c r="B4" s="24">
+        <f>Balance!C14</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Balance (Cr)</t>
         </is>
       </c>
-      <c r="B5" s="20">
-        <f>Balance!D15</f>
+      <c r="B5" s="26">
+        <f>Balance!D14</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="27" t="inlineStr">
         <is>
           <t>Players</t>
         </is>
       </c>
-      <c r="B6" s="22">
-        <f>Balance!E15</f>
+      <c r="B6" s="28">
+        <f>Balance!E14</f>
         <v/>
       </c>
     </row>
@@ -9068,52 +9092,52 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="16">
-        <f>Balance!A16</f>
+      <c r="A1" s="22">
+        <f>Balance!A15</f>
         <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="17" t="inlineStr">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t>Purse (Cr)</t>
         </is>
       </c>
-      <c r="B3" s="18">
-        <f>Balance!B16</f>
+      <c r="B3" s="24">
+        <f>Balance!B15</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="23" t="inlineStr">
         <is>
           <t>Spent (Cr)</t>
         </is>
       </c>
-      <c r="B4" s="18">
-        <f>Balance!C16</f>
+      <c r="B4" s="24">
+        <f>Balance!C15</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Balance (Cr)</t>
         </is>
       </c>
-      <c r="B5" s="20">
-        <f>Balance!D16</f>
+      <c r="B5" s="26">
+        <f>Balance!D15</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="27" t="inlineStr">
         <is>
           <t>Players</t>
         </is>
       </c>
-      <c r="B6" s="22">
-        <f>Balance!E16</f>
+      <c r="B6" s="28">
+        <f>Balance!E15</f>
         <v/>
       </c>
     </row>
@@ -9552,52 +9576,52 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="16">
-        <f>Balance!A17</f>
+      <c r="A1" s="22">
+        <f>Balance!A16</f>
         <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="17" t="inlineStr">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t>Purse (Cr)</t>
         </is>
       </c>
-      <c r="B3" s="18">
-        <f>Balance!B17</f>
+      <c r="B3" s="24">
+        <f>Balance!B16</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="23" t="inlineStr">
         <is>
           <t>Spent (Cr)</t>
         </is>
       </c>
-      <c r="B4" s="18">
-        <f>Balance!C17</f>
+      <c r="B4" s="24">
+        <f>Balance!C16</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Balance (Cr)</t>
         </is>
       </c>
-      <c r="B5" s="20">
-        <f>Balance!D17</f>
+      <c r="B5" s="26">
+        <f>Balance!D16</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="27" t="inlineStr">
         <is>
           <t>Players</t>
         </is>
       </c>
-      <c r="B6" s="22">
-        <f>Balance!E17</f>
+      <c r="B6" s="28">
+        <f>Balance!E16</f>
         <v/>
       </c>
     </row>
@@ -10036,51 +10060,535 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="16">
+      <c r="A1" s="22">
+        <f>Balance!A17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="23" t="inlineStr">
+        <is>
+          <t>Purse (Cr)</t>
+        </is>
+      </c>
+      <c r="B3" s="24">
+        <f>Balance!B17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="23" t="inlineStr">
+        <is>
+          <t>Spent (Cr)</t>
+        </is>
+      </c>
+      <c r="B4" s="24">
+        <f>Balance!C17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="25" t="inlineStr">
+        <is>
+          <t>Balance (Cr)</t>
+        </is>
+      </c>
+      <c r="B5" s="26">
+        <f>Balance!D17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="27" t="inlineStr">
+        <is>
+          <t>Players</t>
+        </is>
+      </c>
+      <c r="B6" s="28">
+        <f>Balance!E17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Price (Cr)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5">
+        <f t="array" ref="A9">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A9))),"")</f>
+        <v/>
+      </c>
+      <c r="B9" s="6">
+        <f t="array" ref="B9">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A9))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9">
+        <f t="array" ref="A10">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A10))),"")</f>
+        <v/>
+      </c>
+      <c r="B10" s="10">
+        <f t="array" ref="B10">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A10))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5">
+        <f t="array" ref="A11">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A11))),"")</f>
+        <v/>
+      </c>
+      <c r="B11" s="6">
+        <f t="array" ref="B11">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A11))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9">
+        <f t="array" ref="A12">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A12))),"")</f>
+        <v/>
+      </c>
+      <c r="B12" s="10">
+        <f t="array" ref="B12">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A12))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5">
+        <f t="array" ref="A13">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A13))),"")</f>
+        <v/>
+      </c>
+      <c r="B13" s="6">
+        <f t="array" ref="B13">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A13))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9">
+        <f t="array" ref="A14">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A14))),"")</f>
+        <v/>
+      </c>
+      <c r="B14" s="10">
+        <f t="array" ref="B14">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A14))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5">
+        <f t="array" ref="A15">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A15))),"")</f>
+        <v/>
+      </c>
+      <c r="B15" s="6">
+        <f t="array" ref="B15">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A15))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9">
+        <f t="array" ref="A16">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A16))),"")</f>
+        <v/>
+      </c>
+      <c r="B16" s="10">
+        <f t="array" ref="B16">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A16))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5">
+        <f t="array" ref="A17">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A17))),"")</f>
+        <v/>
+      </c>
+      <c r="B17" s="6">
+        <f t="array" ref="B17">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A17))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9">
+        <f t="array" ref="A18">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A18))),"")</f>
+        <v/>
+      </c>
+      <c r="B18" s="10">
+        <f t="array" ref="B18">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A18))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5">
+        <f t="array" ref="A19">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A19))),"")</f>
+        <v/>
+      </c>
+      <c r="B19" s="6">
+        <f t="array" ref="B19">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A19))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9">
+        <f t="array" ref="A20">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A20))),"")</f>
+        <v/>
+      </c>
+      <c r="B20" s="10">
+        <f t="array" ref="B20">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A20))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5">
+        <f t="array" ref="A21">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A21))),"")</f>
+        <v/>
+      </c>
+      <c r="B21" s="6">
+        <f t="array" ref="B21">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A21))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9">
+        <f t="array" ref="A22">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A22))),"")</f>
+        <v/>
+      </c>
+      <c r="B22" s="10">
+        <f t="array" ref="B22">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A22))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5">
+        <f t="array" ref="A23">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A23))),"")</f>
+        <v/>
+      </c>
+      <c r="B23" s="6">
+        <f t="array" ref="B23">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A23))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9">
+        <f t="array" ref="A24">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A24))),"")</f>
+        <v/>
+      </c>
+      <c r="B24" s="10">
+        <f t="array" ref="B24">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A24))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5">
+        <f t="array" ref="A25">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A25))),"")</f>
+        <v/>
+      </c>
+      <c r="B25" s="6">
+        <f t="array" ref="B25">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A25))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9">
+        <f t="array" ref="A26">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A26))),"")</f>
+        <v/>
+      </c>
+      <c r="B26" s="10">
+        <f t="array" ref="B26">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A26))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5">
+        <f t="array" ref="A27">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A27))),"")</f>
+        <v/>
+      </c>
+      <c r="B27" s="6">
+        <f t="array" ref="B27">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A27))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9">
+        <f t="array" ref="A28">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A28))),"")</f>
+        <v/>
+      </c>
+      <c r="B28" s="10">
+        <f t="array" ref="B28">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A28))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5">
+        <f t="array" ref="A29">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A29))),"")</f>
+        <v/>
+      </c>
+      <c r="B29" s="6">
+        <f t="array" ref="B29">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A29))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9">
+        <f t="array" ref="A30">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A30))),"")</f>
+        <v/>
+      </c>
+      <c r="B30" s="10">
+        <f t="array" ref="B30">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A30))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5">
+        <f t="array" ref="A31">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A31))),"")</f>
+        <v/>
+      </c>
+      <c r="B31" s="6">
+        <f t="array" ref="B31">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A31))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9">
+        <f t="array" ref="A32">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A32))),"")</f>
+        <v/>
+      </c>
+      <c r="B32" s="10">
+        <f t="array" ref="B32">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A32))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5">
+        <f t="array" ref="A33">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A33))),"")</f>
+        <v/>
+      </c>
+      <c r="B33" s="6">
+        <f t="array" ref="B33">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A33))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9">
+        <f t="array" ref="A34">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A34))),"")</f>
+        <v/>
+      </c>
+      <c r="B34" s="10">
+        <f t="array" ref="B34">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A34))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5">
+        <f t="array" ref="A35">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A35))),"")</f>
+        <v/>
+      </c>
+      <c r="B35" s="6">
+        <f t="array" ref="B35">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A35))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9">
+        <f t="array" ref="A36">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A36))),"")</f>
+        <v/>
+      </c>
+      <c r="B36" s="10">
+        <f t="array" ref="B36">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A36))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5">
+        <f t="array" ref="A37">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A37))),"")</f>
+        <v/>
+      </c>
+      <c r="B37" s="6">
+        <f t="array" ref="B37">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A37))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="9">
+        <f t="array" ref="A38">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A38))),"")</f>
+        <v/>
+      </c>
+      <c r="B38" s="10">
+        <f t="array" ref="B38">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A38))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5">
+        <f t="array" ref="A39">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A39))),"")</f>
+        <v/>
+      </c>
+      <c r="B39" s="6">
+        <f t="array" ref="B39">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A39))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9">
+        <f t="array" ref="A40">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A40))),"")</f>
+        <v/>
+      </c>
+      <c r="B40" s="10">
+        <f t="array" ref="B40">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A40))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5">
+        <f t="array" ref="A41">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A41))),"")</f>
+        <v/>
+      </c>
+      <c r="B41" s="6">
+        <f t="array" ref="B41">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A41))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="9">
+        <f t="array" ref="A42">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A42))),"")</f>
+        <v/>
+      </c>
+      <c r="B42" s="10">
+        <f t="array" ref="B42">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A42))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5">
+        <f t="array" ref="A43">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A43))),"")</f>
+        <v/>
+      </c>
+      <c r="B43" s="6">
+        <f t="array" ref="B43">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A43))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="9">
+        <f t="array" ref="A44">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A44))),"")</f>
+        <v/>
+      </c>
+      <c r="B44" s="10">
+        <f t="array" ref="B44">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A44))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5">
+        <f t="array" ref="A45">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A45))),"")</f>
+        <v/>
+      </c>
+      <c r="B45" s="6">
+        <f t="array" ref="B45">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A45))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="9">
+        <f t="array" ref="A46">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A46))),"")</f>
+        <v/>
+      </c>
+      <c r="B46" s="10">
+        <f t="array" ref="B46">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A46))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5">
+        <f t="array" ref="A47">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A47))),"")</f>
+        <v/>
+      </c>
+      <c r="B47" s="6">
+        <f t="array" ref="B47">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A47))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="9">
+        <f t="array" ref="A48">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A48))),"")</f>
+        <v/>
+      </c>
+      <c r="B48" s="10">
+        <f t="array" ref="B48">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A48))),"")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="002E5E8C"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="22">
         <f>Balance!A18</f>
         <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="17" t="inlineStr">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t>Purse (Cr)</t>
         </is>
       </c>
-      <c r="B3" s="18">
+      <c r="B3" s="24">
         <f>Balance!B18</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="23" t="inlineStr">
         <is>
           <t>Spent (Cr)</t>
         </is>
       </c>
-      <c r="B4" s="18">
+      <c r="B4" s="24">
         <f>Balance!C18</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Balance (Cr)</t>
         </is>
       </c>
-      <c r="B5" s="20">
+      <c r="B5" s="26">
         <f>Balance!D18</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="27" t="inlineStr">
         <is>
           <t>Players</t>
         </is>
       </c>
-      <c r="B6" s="22">
+      <c r="B6" s="28">
         <f>Balance!E18</f>
         <v/>
       </c>
@@ -10928,482 +11436,3382 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002E5E8C"/>
+    <tabColor rgb="002E7D32"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B48"/>
+  <dimension ref="B2:T63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="2" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="2" customWidth="1" min="9" max="9"/>
+    <col width="5" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="2" customWidth="1" min="13" max="13"/>
+    <col width="5" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="9" customWidth="1" min="16" max="16"/>
+    <col width="2" customWidth="1" min="17" max="17"/>
+    <col width="5" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
+    <col width="9" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="16">
-        <f>Balance!A4</f>
+    <row r="2" ht="22" customHeight="1">
+      <c r="B2" s="16">
+        <f>Balance!$A$4</f>
+        <v/>
+      </c>
+      <c r="F2" s="16">
+        <f>Balance!$A$5</f>
+        <v/>
+      </c>
+      <c r="J2" s="16">
+        <f>Balance!$A$6</f>
+        <v/>
+      </c>
+      <c r="N2" s="16">
+        <f>Balance!$A$7</f>
+        <v/>
+      </c>
+      <c r="R2" s="16">
+        <f>Balance!$A$8</f>
         <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="17" t="inlineStr">
-        <is>
-          <t>Purse (Cr)</t>
-        </is>
-      </c>
-      <c r="B3" s="18">
-        <f>Balance!B4</f>
-        <v/>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>S.No</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Player Name</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>S.No</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Player Name</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>S.No</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>Player Name</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>S.No</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>Player Name</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>S.No</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr">
+        <is>
+          <t>Player Name</t>
+        </is>
+      </c>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
-        <is>
-          <t>Spent (Cr)</t>
-        </is>
-      </c>
-      <c r="B4" s="18">
-        <f>Balance!C4</f>
+      <c r="B4" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="5">
+        <f t="array" ref="C4">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),1)),"")</f>
+        <v/>
+      </c>
+      <c r="D4" s="6">
+        <f t="array" ref="D4">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),1)),"")</f>
+        <v/>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="5">
+        <f t="array" ref="G4">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),1)),"")</f>
+        <v/>
+      </c>
+      <c r="H4" s="6">
+        <f t="array" ref="H4">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),1)),"")</f>
+        <v/>
+      </c>
+      <c r="J4" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" s="5">
+        <f t="array" ref="K4">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),1)),"")</f>
+        <v/>
+      </c>
+      <c r="L4" s="6">
+        <f t="array" ref="L4">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),1)),"")</f>
+        <v/>
+      </c>
+      <c r="N4" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" s="5">
+        <f t="array" ref="O4">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),1)),"")</f>
+        <v/>
+      </c>
+      <c r="P4" s="6">
+        <f t="array" ref="P4">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),1)),"")</f>
+        <v/>
+      </c>
+      <c r="R4" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <f t="array" ref="S4">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),1)),"")</f>
+        <v/>
+      </c>
+      <c r="T4" s="6">
+        <f t="array" ref="T4">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),1)),"")</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="inlineStr">
-        <is>
-          <t>Balance (Cr)</t>
-        </is>
-      </c>
-      <c r="B5" s="20">
-        <f>Balance!D4</f>
+      <c r="B5" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="9">
+        <f t="array" ref="C5">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),2)),"")</f>
+        <v/>
+      </c>
+      <c r="D5" s="10">
+        <f t="array" ref="D5">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),2)),"")</f>
+        <v/>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" s="9">
+        <f t="array" ref="G5">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),2)),"")</f>
+        <v/>
+      </c>
+      <c r="H5" s="10">
+        <f t="array" ref="H5">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),2)),"")</f>
+        <v/>
+      </c>
+      <c r="J5" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" s="9">
+        <f t="array" ref="K5">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),2)),"")</f>
+        <v/>
+      </c>
+      <c r="L5" s="10">
+        <f t="array" ref="L5">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),2)),"")</f>
+        <v/>
+      </c>
+      <c r="N5" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="O5" s="9">
+        <f t="array" ref="O5">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),2)),"")</f>
+        <v/>
+      </c>
+      <c r="P5" s="10">
+        <f t="array" ref="P5">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),2)),"")</f>
+        <v/>
+      </c>
+      <c r="R5" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="S5" s="9">
+        <f t="array" ref="S5">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),2)),"")</f>
+        <v/>
+      </c>
+      <c r="T5" s="10">
+        <f t="array" ref="T5">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),2)),"")</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="inlineStr">
-        <is>
-          <t>Players</t>
-        </is>
-      </c>
-      <c r="B6" s="22">
-        <f>Balance!E4</f>
+      <c r="B6" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" s="5">
+        <f t="array" ref="C6">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),3)),"")</f>
+        <v/>
+      </c>
+      <c r="D6" s="6">
+        <f t="array" ref="D6">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),3)),"")</f>
+        <v/>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" s="5">
+        <f t="array" ref="G6">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),3)),"")</f>
+        <v/>
+      </c>
+      <c r="H6" s="6">
+        <f t="array" ref="H6">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),3)),"")</f>
+        <v/>
+      </c>
+      <c r="J6" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K6" s="5">
+        <f t="array" ref="K6">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),3)),"")</f>
+        <v/>
+      </c>
+      <c r="L6" s="6">
+        <f t="array" ref="L6">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),3)),"")</f>
+        <v/>
+      </c>
+      <c r="N6" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="O6" s="5">
+        <f t="array" ref="O6">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),3)),"")</f>
+        <v/>
+      </c>
+      <c r="P6" s="6">
+        <f t="array" ref="P6">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),3)),"")</f>
+        <v/>
+      </c>
+      <c r="R6" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="S6" s="5">
+        <f t="array" ref="S6">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),3)),"")</f>
+        <v/>
+      </c>
+      <c r="T6" s="6">
+        <f t="array" ref="T6">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),3)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" s="9">
+        <f t="array" ref="C7">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),4)),"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="10">
+        <f t="array" ref="D7">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),4)),"")</f>
+        <v/>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="G7" s="9">
+        <f t="array" ref="G7">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),4)),"")</f>
+        <v/>
+      </c>
+      <c r="H7" s="10">
+        <f t="array" ref="H7">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),4)),"")</f>
+        <v/>
+      </c>
+      <c r="J7" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K7" s="9">
+        <f t="array" ref="K7">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),4)),"")</f>
+        <v/>
+      </c>
+      <c r="L7" s="10">
+        <f t="array" ref="L7">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),4)),"")</f>
+        <v/>
+      </c>
+      <c r="N7" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="O7" s="9">
+        <f t="array" ref="O7">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),4)),"")</f>
+        <v/>
+      </c>
+      <c r="P7" s="10">
+        <f t="array" ref="P7">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),4)),"")</f>
+        <v/>
+      </c>
+      <c r="R7" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="S7" s="9">
+        <f t="array" ref="S7">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),4)),"")</f>
+        <v/>
+      </c>
+      <c r="T7" s="10">
+        <f t="array" ref="T7">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),4)),"")</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Player</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Price (Cr)</t>
-        </is>
+      <c r="B8" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" s="5">
+        <f t="array" ref="C8">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),5)),"")</f>
+        <v/>
+      </c>
+      <c r="D8" s="6">
+        <f t="array" ref="D8">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),5)),"")</f>
+        <v/>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" s="5">
+        <f t="array" ref="G8">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),5)),"")</f>
+        <v/>
+      </c>
+      <c r="H8" s="6">
+        <f t="array" ref="H8">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),5)),"")</f>
+        <v/>
+      </c>
+      <c r="J8" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K8" s="5">
+        <f t="array" ref="K8">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),5)),"")</f>
+        <v/>
+      </c>
+      <c r="L8" s="6">
+        <f t="array" ref="L8">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),5)),"")</f>
+        <v/>
+      </c>
+      <c r="N8" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="O8" s="5">
+        <f t="array" ref="O8">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),5)),"")</f>
+        <v/>
+      </c>
+      <c r="P8" s="6">
+        <f t="array" ref="P8">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),5)),"")</f>
+        <v/>
+      </c>
+      <c r="R8" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="S8" s="5">
+        <f t="array" ref="S8">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),5)),"")</f>
+        <v/>
+      </c>
+      <c r="T8" s="6">
+        <f t="array" ref="T8">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),5)),"")</f>
+        <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5">
-        <f t="array" ref="A9">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A9))),"")</f>
-        <v/>
-      </c>
-      <c r="B9" s="6">
-        <f t="array" ref="B9">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A9))),"")</f>
+      <c r="B9" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C9" s="9">
+        <f t="array" ref="C9">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),6)),"")</f>
+        <v/>
+      </c>
+      <c r="D9" s="10">
+        <f t="array" ref="D9">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),6)),"")</f>
+        <v/>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="G9" s="9">
+        <f t="array" ref="G9">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),6)),"")</f>
+        <v/>
+      </c>
+      <c r="H9" s="10">
+        <f t="array" ref="H9">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),6)),"")</f>
+        <v/>
+      </c>
+      <c r="J9" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="K9" s="9">
+        <f t="array" ref="K9">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),6)),"")</f>
+        <v/>
+      </c>
+      <c r="L9" s="10">
+        <f t="array" ref="L9">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),6)),"")</f>
+        <v/>
+      </c>
+      <c r="N9" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="O9" s="9">
+        <f t="array" ref="O9">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),6)),"")</f>
+        <v/>
+      </c>
+      <c r="P9" s="10">
+        <f t="array" ref="P9">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),6)),"")</f>
+        <v/>
+      </c>
+      <c r="R9" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="S9" s="9">
+        <f t="array" ref="S9">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),6)),"")</f>
+        <v/>
+      </c>
+      <c r="T9" s="10">
+        <f t="array" ref="T9">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),6)),"")</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9">
-        <f t="array" ref="A10">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A10))),"")</f>
-        <v/>
-      </c>
-      <c r="B10" s="10">
-        <f t="array" ref="B10">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A10))),"")</f>
+      <c r="B10" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C10" s="5">
+        <f t="array" ref="C10">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),7)),"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="6">
+        <f t="array" ref="D10">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),7)),"")</f>
+        <v/>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="G10" s="5">
+        <f t="array" ref="G10">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),7)),"")</f>
+        <v/>
+      </c>
+      <c r="H10" s="6">
+        <f t="array" ref="H10">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),7)),"")</f>
+        <v/>
+      </c>
+      <c r="J10" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="K10" s="5">
+        <f t="array" ref="K10">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),7)),"")</f>
+        <v/>
+      </c>
+      <c r="L10" s="6">
+        <f t="array" ref="L10">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),7)),"")</f>
+        <v/>
+      </c>
+      <c r="N10" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="O10" s="5">
+        <f t="array" ref="O10">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),7)),"")</f>
+        <v/>
+      </c>
+      <c r="P10" s="6">
+        <f t="array" ref="P10">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),7)),"")</f>
+        <v/>
+      </c>
+      <c r="R10" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="S10" s="5">
+        <f t="array" ref="S10">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),7)),"")</f>
+        <v/>
+      </c>
+      <c r="T10" s="6">
+        <f t="array" ref="T10">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),7)),"")</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5">
-        <f t="array" ref="A11">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A11))),"")</f>
-        <v/>
-      </c>
-      <c r="B11" s="6">
-        <f t="array" ref="B11">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A11))),"")</f>
+      <c r="B11" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="C11" s="9">
+        <f t="array" ref="C11">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),8)),"")</f>
+        <v/>
+      </c>
+      <c r="D11" s="10">
+        <f t="array" ref="D11">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),8)),"")</f>
+        <v/>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="G11" s="9">
+        <f t="array" ref="G11">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),8)),"")</f>
+        <v/>
+      </c>
+      <c r="H11" s="10">
+        <f t="array" ref="H11">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),8)),"")</f>
+        <v/>
+      </c>
+      <c r="J11" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="K11" s="9">
+        <f t="array" ref="K11">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),8)),"")</f>
+        <v/>
+      </c>
+      <c r="L11" s="10">
+        <f t="array" ref="L11">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),8)),"")</f>
+        <v/>
+      </c>
+      <c r="N11" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="O11" s="9">
+        <f t="array" ref="O11">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),8)),"")</f>
+        <v/>
+      </c>
+      <c r="P11" s="10">
+        <f t="array" ref="P11">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),8)),"")</f>
+        <v/>
+      </c>
+      <c r="R11" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="S11" s="9">
+        <f t="array" ref="S11">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),8)),"")</f>
+        <v/>
+      </c>
+      <c r="T11" s="10">
+        <f t="array" ref="T11">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),8)),"")</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9">
-        <f t="array" ref="A12">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A12))),"")</f>
-        <v/>
-      </c>
-      <c r="B12" s="10">
-        <f t="array" ref="B12">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A12))),"")</f>
+      <c r="B12" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="C12" s="5">
+        <f t="array" ref="C12">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),9)),"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="6">
+        <f t="array" ref="D12">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),9)),"")</f>
+        <v/>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="G12" s="5">
+        <f t="array" ref="G12">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),9)),"")</f>
+        <v/>
+      </c>
+      <c r="H12" s="6">
+        <f t="array" ref="H12">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),9)),"")</f>
+        <v/>
+      </c>
+      <c r="J12" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="K12" s="5">
+        <f t="array" ref="K12">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),9)),"")</f>
+        <v/>
+      </c>
+      <c r="L12" s="6">
+        <f t="array" ref="L12">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),9)),"")</f>
+        <v/>
+      </c>
+      <c r="N12" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="O12" s="5">
+        <f t="array" ref="O12">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),9)),"")</f>
+        <v/>
+      </c>
+      <c r="P12" s="6">
+        <f t="array" ref="P12">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),9)),"")</f>
+        <v/>
+      </c>
+      <c r="R12" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="S12" s="5">
+        <f t="array" ref="S12">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),9)),"")</f>
+        <v/>
+      </c>
+      <c r="T12" s="6">
+        <f t="array" ref="T12">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),9)),"")</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5">
-        <f t="array" ref="A13">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A13))),"")</f>
-        <v/>
-      </c>
-      <c r="B13" s="6">
-        <f t="array" ref="B13">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A13))),"")</f>
+      <c r="B13" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C13" s="9">
+        <f t="array" ref="C13">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),10)),"")</f>
+        <v/>
+      </c>
+      <c r="D13" s="10">
+        <f t="array" ref="D13">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),10)),"")</f>
+        <v/>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" s="9">
+        <f t="array" ref="G13">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),10)),"")</f>
+        <v/>
+      </c>
+      <c r="H13" s="10">
+        <f t="array" ref="H13">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),10)),"")</f>
+        <v/>
+      </c>
+      <c r="J13" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="K13" s="9">
+        <f t="array" ref="K13">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),10)),"")</f>
+        <v/>
+      </c>
+      <c r="L13" s="10">
+        <f t="array" ref="L13">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),10)),"")</f>
+        <v/>
+      </c>
+      <c r="N13" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="O13" s="9">
+        <f t="array" ref="O13">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),10)),"")</f>
+        <v/>
+      </c>
+      <c r="P13" s="10">
+        <f t="array" ref="P13">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),10)),"")</f>
+        <v/>
+      </c>
+      <c r="R13" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="S13" s="9">
+        <f t="array" ref="S13">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),10)),"")</f>
+        <v/>
+      </c>
+      <c r="T13" s="10">
+        <f t="array" ref="T13">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),10)),"")</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9">
-        <f t="array" ref="A14">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A14))),"")</f>
-        <v/>
-      </c>
-      <c r="B14" s="10">
-        <f t="array" ref="B14">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A14))),"")</f>
+      <c r="B14" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="C14" s="5">
+        <f t="array" ref="C14">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),11)),"")</f>
+        <v/>
+      </c>
+      <c r="D14" s="6">
+        <f t="array" ref="D14">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),11)),"")</f>
+        <v/>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="G14" s="5">
+        <f t="array" ref="G14">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),11)),"")</f>
+        <v/>
+      </c>
+      <c r="H14" s="6">
+        <f t="array" ref="H14">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),11)),"")</f>
+        <v/>
+      </c>
+      <c r="J14" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="K14" s="5">
+        <f t="array" ref="K14">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),11)),"")</f>
+        <v/>
+      </c>
+      <c r="L14" s="6">
+        <f t="array" ref="L14">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),11)),"")</f>
+        <v/>
+      </c>
+      <c r="N14" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="O14" s="5">
+        <f t="array" ref="O14">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),11)),"")</f>
+        <v/>
+      </c>
+      <c r="P14" s="6">
+        <f t="array" ref="P14">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),11)),"")</f>
+        <v/>
+      </c>
+      <c r="R14" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="S14" s="5">
+        <f t="array" ref="S14">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),11)),"")</f>
+        <v/>
+      </c>
+      <c r="T14" s="6">
+        <f t="array" ref="T14">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),11)),"")</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5">
-        <f t="array" ref="A15">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A15))),"")</f>
-        <v/>
-      </c>
-      <c r="B15" s="6">
-        <f t="array" ref="B15">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A15))),"")</f>
+      <c r="B15" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="C15" s="9">
+        <f t="array" ref="C15">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),12)),"")</f>
+        <v/>
+      </c>
+      <c r="D15" s="10">
+        <f t="array" ref="D15">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),12)),"")</f>
+        <v/>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="G15" s="9">
+        <f t="array" ref="G15">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),12)),"")</f>
+        <v/>
+      </c>
+      <c r="H15" s="10">
+        <f t="array" ref="H15">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),12)),"")</f>
+        <v/>
+      </c>
+      <c r="J15" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="K15" s="9">
+        <f t="array" ref="K15">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),12)),"")</f>
+        <v/>
+      </c>
+      <c r="L15" s="10">
+        <f t="array" ref="L15">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),12)),"")</f>
+        <v/>
+      </c>
+      <c r="N15" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="O15" s="9">
+        <f t="array" ref="O15">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),12)),"")</f>
+        <v/>
+      </c>
+      <c r="P15" s="10">
+        <f t="array" ref="P15">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),12)),"")</f>
+        <v/>
+      </c>
+      <c r="R15" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="S15" s="9">
+        <f t="array" ref="S15">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),12)),"")</f>
+        <v/>
+      </c>
+      <c r="T15" s="10">
+        <f t="array" ref="T15">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),12)),"")</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9">
-        <f t="array" ref="A16">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A16))),"")</f>
-        <v/>
-      </c>
-      <c r="B16" s="10">
-        <f t="array" ref="B16">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A16))),"")</f>
+      <c r="B16" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="C16" s="5">
+        <f t="array" ref="C16">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),13)),"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="6">
+        <f t="array" ref="D16">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),13)),"")</f>
+        <v/>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="G16" s="5">
+        <f t="array" ref="G16">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),13)),"")</f>
+        <v/>
+      </c>
+      <c r="H16" s="6">
+        <f t="array" ref="H16">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),13)),"")</f>
+        <v/>
+      </c>
+      <c r="J16" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="K16" s="5">
+        <f t="array" ref="K16">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),13)),"")</f>
+        <v/>
+      </c>
+      <c r="L16" s="6">
+        <f t="array" ref="L16">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),13)),"")</f>
+        <v/>
+      </c>
+      <c r="N16" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="O16" s="5">
+        <f t="array" ref="O16">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),13)),"")</f>
+        <v/>
+      </c>
+      <c r="P16" s="6">
+        <f t="array" ref="P16">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),13)),"")</f>
+        <v/>
+      </c>
+      <c r="R16" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="S16" s="5">
+        <f t="array" ref="S16">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),13)),"")</f>
+        <v/>
+      </c>
+      <c r="T16" s="6">
+        <f t="array" ref="T16">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),13)),"")</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5">
-        <f t="array" ref="A17">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A17))),"")</f>
-        <v/>
-      </c>
-      <c r="B17" s="6">
-        <f t="array" ref="B17">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A17))),"")</f>
+      <c r="B17" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="C17" s="9">
+        <f t="array" ref="C17">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),14)),"")</f>
+        <v/>
+      </c>
+      <c r="D17" s="10">
+        <f t="array" ref="D17">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),14)),"")</f>
+        <v/>
+      </c>
+      <c r="F17" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="G17" s="9">
+        <f t="array" ref="G17">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),14)),"")</f>
+        <v/>
+      </c>
+      <c r="H17" s="10">
+        <f t="array" ref="H17">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),14)),"")</f>
+        <v/>
+      </c>
+      <c r="J17" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="K17" s="9">
+        <f t="array" ref="K17">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),14)),"")</f>
+        <v/>
+      </c>
+      <c r="L17" s="10">
+        <f t="array" ref="L17">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),14)),"")</f>
+        <v/>
+      </c>
+      <c r="N17" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="O17" s="9">
+        <f t="array" ref="O17">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),14)),"")</f>
+        <v/>
+      </c>
+      <c r="P17" s="10">
+        <f t="array" ref="P17">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),14)),"")</f>
+        <v/>
+      </c>
+      <c r="R17" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="S17" s="9">
+        <f t="array" ref="S17">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),14)),"")</f>
+        <v/>
+      </c>
+      <c r="T17" s="10">
+        <f t="array" ref="T17">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),14)),"")</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9">
-        <f t="array" ref="A18">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A18))),"")</f>
-        <v/>
-      </c>
-      <c r="B18" s="10">
-        <f t="array" ref="B18">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A18))),"")</f>
+      <c r="B18" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="C18" s="5">
+        <f t="array" ref="C18">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),15)),"")</f>
+        <v/>
+      </c>
+      <c r="D18" s="6">
+        <f t="array" ref="D18">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),15)),"")</f>
+        <v/>
+      </c>
+      <c r="F18" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="G18" s="5">
+        <f t="array" ref="G18">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),15)),"")</f>
+        <v/>
+      </c>
+      <c r="H18" s="6">
+        <f t="array" ref="H18">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),15)),"")</f>
+        <v/>
+      </c>
+      <c r="J18" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="K18" s="5">
+        <f t="array" ref="K18">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),15)),"")</f>
+        <v/>
+      </c>
+      <c r="L18" s="6">
+        <f t="array" ref="L18">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),15)),"")</f>
+        <v/>
+      </c>
+      <c r="N18" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="O18" s="5">
+        <f t="array" ref="O18">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),15)),"")</f>
+        <v/>
+      </c>
+      <c r="P18" s="6">
+        <f t="array" ref="P18">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),15)),"")</f>
+        <v/>
+      </c>
+      <c r="R18" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="S18" s="5">
+        <f t="array" ref="S18">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),15)),"")</f>
+        <v/>
+      </c>
+      <c r="T18" s="6">
+        <f t="array" ref="T18">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$2,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),15)),"")</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5">
-        <f t="array" ref="A19">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A19))),"")</f>
-        <v/>
-      </c>
-      <c r="B19" s="6">
-        <f t="array" ref="B19">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A19))),"")</f>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>Total Amount Spent</t>
+        </is>
+      </c>
+      <c r="D19" s="18">
+        <f>Balance!$C$4</f>
+        <v/>
+      </c>
+      <c r="F19" s="17" t="inlineStr">
+        <is>
+          <t>Total Amount Spent</t>
+        </is>
+      </c>
+      <c r="H19" s="18">
+        <f>Balance!$C$5</f>
+        <v/>
+      </c>
+      <c r="J19" s="17" t="inlineStr">
+        <is>
+          <t>Total Amount Spent</t>
+        </is>
+      </c>
+      <c r="L19" s="18">
+        <f>Balance!$C$6</f>
+        <v/>
+      </c>
+      <c r="N19" s="17" t="inlineStr">
+        <is>
+          <t>Total Amount Spent</t>
+        </is>
+      </c>
+      <c r="P19" s="18">
+        <f>Balance!$C$7</f>
+        <v/>
+      </c>
+      <c r="R19" s="17" t="inlineStr">
+        <is>
+          <t>Total Amount Spent</t>
+        </is>
+      </c>
+      <c r="T19" s="18">
+        <f>Balance!$C$8</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="9">
-        <f t="array" ref="A20">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A20))),"")</f>
-        <v/>
-      </c>
-      <c r="B20" s="10">
-        <f t="array" ref="B20">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A20))),"")</f>
+      <c r="B20" s="19" t="inlineStr">
+        <is>
+          <t>Total Amount Left</t>
+        </is>
+      </c>
+      <c r="D20" s="20">
+        <f>Balance!$D$4</f>
+        <v/>
+      </c>
+      <c r="F20" s="19" t="inlineStr">
+        <is>
+          <t>Total Amount Left</t>
+        </is>
+      </c>
+      <c r="H20" s="20">
+        <f>Balance!$D$5</f>
+        <v/>
+      </c>
+      <c r="J20" s="19" t="inlineStr">
+        <is>
+          <t>Total Amount Left</t>
+        </is>
+      </c>
+      <c r="L20" s="20">
+        <f>Balance!$D$6</f>
+        <v/>
+      </c>
+      <c r="N20" s="19" t="inlineStr">
+        <is>
+          <t>Total Amount Left</t>
+        </is>
+      </c>
+      <c r="P20" s="20">
+        <f>Balance!$D$7</f>
+        <v/>
+      </c>
+      <c r="R20" s="19" t="inlineStr">
+        <is>
+          <t>Total Amount Left</t>
+        </is>
+      </c>
+      <c r="T20" s="20">
+        <f>Balance!$D$8</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5">
-        <f t="array" ref="A21">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A21))),"")</f>
-        <v/>
-      </c>
-      <c r="B21" s="6">
-        <f t="array" ref="B21">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A21))),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="9">
-        <f t="array" ref="A22">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A22))),"")</f>
-        <v/>
-      </c>
-      <c r="B22" s="10">
-        <f t="array" ref="B22">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A22))),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5">
-        <f t="array" ref="A23">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A23))),"")</f>
-        <v/>
-      </c>
-      <c r="B23" s="6">
-        <f t="array" ref="B23">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A23))),"")</f>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>Total Amount</t>
+        </is>
+      </c>
+      <c r="D21" s="14">
+        <f>Balance!$B$4</f>
+        <v/>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
+        <is>
+          <t>Total Amount</t>
+        </is>
+      </c>
+      <c r="H21" s="14">
+        <f>Balance!$B$5</f>
+        <v/>
+      </c>
+      <c r="J21" s="21" t="inlineStr">
+        <is>
+          <t>Total Amount</t>
+        </is>
+      </c>
+      <c r="L21" s="14">
+        <f>Balance!$B$6</f>
+        <v/>
+      </c>
+      <c r="N21" s="21" t="inlineStr">
+        <is>
+          <t>Total Amount</t>
+        </is>
+      </c>
+      <c r="P21" s="14">
+        <f>Balance!$B$7</f>
+        <v/>
+      </c>
+      <c r="R21" s="21" t="inlineStr">
+        <is>
+          <t>Total Amount</t>
+        </is>
+      </c>
+      <c r="T21" s="14">
+        <f>Balance!$B$8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="B23" s="16">
+        <f>Balance!$A$9</f>
+        <v/>
+      </c>
+      <c r="F23" s="16">
+        <f>Balance!$A$10</f>
+        <v/>
+      </c>
+      <c r="J23" s="16">
+        <f>Balance!$A$11</f>
+        <v/>
+      </c>
+      <c r="N23" s="16">
+        <f>Balance!$A$12</f>
+        <v/>
+      </c>
+      <c r="R23" s="16">
+        <f>Balance!$A$13</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="9">
-        <f t="array" ref="A24">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A24))),"")</f>
-        <v/>
-      </c>
-      <c r="B24" s="10">
-        <f t="array" ref="B24">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A24))),"")</f>
-        <v/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>S.No</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Player Name</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>S.No</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Player Name</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>S.No</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>Player Name</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>S.No</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>Player Name</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t>S.No</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="inlineStr">
+        <is>
+          <t>Player Name</t>
+        </is>
+      </c>
+      <c r="T24" s="3" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5">
-        <f t="array" ref="A25">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A25))),"")</f>
-        <v/>
-      </c>
-      <c r="B25" s="6">
-        <f t="array" ref="B25">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A25))),"")</f>
+      <c r="B25" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="5">
+        <f t="array" ref="C25">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),1)),"")</f>
+        <v/>
+      </c>
+      <c r="D25" s="6">
+        <f t="array" ref="D25">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),1)),"")</f>
+        <v/>
+      </c>
+      <c r="F25" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="5">
+        <f t="array" ref="G25">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),1)),"")</f>
+        <v/>
+      </c>
+      <c r="H25" s="6">
+        <f t="array" ref="H25">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),1)),"")</f>
+        <v/>
+      </c>
+      <c r="J25" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" s="5">
+        <f t="array" ref="K25">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),1)),"")</f>
+        <v/>
+      </c>
+      <c r="L25" s="6">
+        <f t="array" ref="L25">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),1)),"")</f>
+        <v/>
+      </c>
+      <c r="N25" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" s="5">
+        <f t="array" ref="O25">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),1)),"")</f>
+        <v/>
+      </c>
+      <c r="P25" s="6">
+        <f t="array" ref="P25">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),1)),"")</f>
+        <v/>
+      </c>
+      <c r="R25" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S25" s="5">
+        <f t="array" ref="S25">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),1)),"")</f>
+        <v/>
+      </c>
+      <c r="T25" s="6">
+        <f t="array" ref="T25">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),1)),"")</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="9">
-        <f t="array" ref="A26">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A26))),"")</f>
-        <v/>
-      </c>
-      <c r="B26" s="10">
-        <f t="array" ref="B26">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A26))),"")</f>
+      <c r="B26" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C26" s="9">
+        <f t="array" ref="C26">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),2)),"")</f>
+        <v/>
+      </c>
+      <c r="D26" s="10">
+        <f t="array" ref="D26">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),2)),"")</f>
+        <v/>
+      </c>
+      <c r="F26" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G26" s="9">
+        <f t="array" ref="G26">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),2)),"")</f>
+        <v/>
+      </c>
+      <c r="H26" s="10">
+        <f t="array" ref="H26">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),2)),"")</f>
+        <v/>
+      </c>
+      <c r="J26" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K26" s="9">
+        <f t="array" ref="K26">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),2)),"")</f>
+        <v/>
+      </c>
+      <c r="L26" s="10">
+        <f t="array" ref="L26">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),2)),"")</f>
+        <v/>
+      </c>
+      <c r="N26" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="O26" s="9">
+        <f t="array" ref="O26">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),2)),"")</f>
+        <v/>
+      </c>
+      <c r="P26" s="10">
+        <f t="array" ref="P26">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),2)),"")</f>
+        <v/>
+      </c>
+      <c r="R26" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="S26" s="9">
+        <f t="array" ref="S26">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),2)),"")</f>
+        <v/>
+      </c>
+      <c r="T26" s="10">
+        <f t="array" ref="T26">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),2)),"")</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5">
-        <f t="array" ref="A27">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A27))),"")</f>
-        <v/>
-      </c>
-      <c r="B27" s="6">
-        <f t="array" ref="B27">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A27))),"")</f>
+      <c r="B27" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C27" s="5">
+        <f t="array" ref="C27">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),3)),"")</f>
+        <v/>
+      </c>
+      <c r="D27" s="6">
+        <f t="array" ref="D27">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),3)),"")</f>
+        <v/>
+      </c>
+      <c r="F27" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G27" s="5">
+        <f t="array" ref="G27">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),3)),"")</f>
+        <v/>
+      </c>
+      <c r="H27" s="6">
+        <f t="array" ref="H27">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),3)),"")</f>
+        <v/>
+      </c>
+      <c r="J27" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K27" s="5">
+        <f t="array" ref="K27">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),3)),"")</f>
+        <v/>
+      </c>
+      <c r="L27" s="6">
+        <f t="array" ref="L27">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),3)),"")</f>
+        <v/>
+      </c>
+      <c r="N27" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="O27" s="5">
+        <f t="array" ref="O27">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),3)),"")</f>
+        <v/>
+      </c>
+      <c r="P27" s="6">
+        <f t="array" ref="P27">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),3)),"")</f>
+        <v/>
+      </c>
+      <c r="R27" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="S27" s="5">
+        <f t="array" ref="S27">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),3)),"")</f>
+        <v/>
+      </c>
+      <c r="T27" s="6">
+        <f t="array" ref="T27">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),3)),"")</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="9">
-        <f t="array" ref="A28">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A28))),"")</f>
-        <v/>
-      </c>
-      <c r="B28" s="10">
-        <f t="array" ref="B28">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A28))),"")</f>
+      <c r="B28" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C28" s="9">
+        <f t="array" ref="C28">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),4)),"")</f>
+        <v/>
+      </c>
+      <c r="D28" s="10">
+        <f t="array" ref="D28">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),4)),"")</f>
+        <v/>
+      </c>
+      <c r="F28" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="G28" s="9">
+        <f t="array" ref="G28">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),4)),"")</f>
+        <v/>
+      </c>
+      <c r="H28" s="10">
+        <f t="array" ref="H28">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),4)),"")</f>
+        <v/>
+      </c>
+      <c r="J28" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K28" s="9">
+        <f t="array" ref="K28">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),4)),"")</f>
+        <v/>
+      </c>
+      <c r="L28" s="10">
+        <f t="array" ref="L28">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),4)),"")</f>
+        <v/>
+      </c>
+      <c r="N28" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="O28" s="9">
+        <f t="array" ref="O28">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),4)),"")</f>
+        <v/>
+      </c>
+      <c r="P28" s="10">
+        <f t="array" ref="P28">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),4)),"")</f>
+        <v/>
+      </c>
+      <c r="R28" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="S28" s="9">
+        <f t="array" ref="S28">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),4)),"")</f>
+        <v/>
+      </c>
+      <c r="T28" s="10">
+        <f t="array" ref="T28">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),4)),"")</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5">
-        <f t="array" ref="A29">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A29))),"")</f>
-        <v/>
-      </c>
-      <c r="B29" s="6">
-        <f t="array" ref="B29">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A29))),"")</f>
+      <c r="B29" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C29" s="5">
+        <f t="array" ref="C29">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),5)),"")</f>
+        <v/>
+      </c>
+      <c r="D29" s="6">
+        <f t="array" ref="D29">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),5)),"")</f>
+        <v/>
+      </c>
+      <c r="F29" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G29" s="5">
+        <f t="array" ref="G29">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),5)),"")</f>
+        <v/>
+      </c>
+      <c r="H29" s="6">
+        <f t="array" ref="H29">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),5)),"")</f>
+        <v/>
+      </c>
+      <c r="J29" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K29" s="5">
+        <f t="array" ref="K29">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),5)),"")</f>
+        <v/>
+      </c>
+      <c r="L29" s="6">
+        <f t="array" ref="L29">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),5)),"")</f>
+        <v/>
+      </c>
+      <c r="N29" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="O29" s="5">
+        <f t="array" ref="O29">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),5)),"")</f>
+        <v/>
+      </c>
+      <c r="P29" s="6">
+        <f t="array" ref="P29">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),5)),"")</f>
+        <v/>
+      </c>
+      <c r="R29" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="S29" s="5">
+        <f t="array" ref="S29">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),5)),"")</f>
+        <v/>
+      </c>
+      <c r="T29" s="6">
+        <f t="array" ref="T29">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),5)),"")</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="9">
-        <f t="array" ref="A30">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A30))),"")</f>
-        <v/>
-      </c>
-      <c r="B30" s="10">
-        <f t="array" ref="B30">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A30))),"")</f>
+      <c r="B30" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C30" s="9">
+        <f t="array" ref="C30">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),6)),"")</f>
+        <v/>
+      </c>
+      <c r="D30" s="10">
+        <f t="array" ref="D30">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),6)),"")</f>
+        <v/>
+      </c>
+      <c r="F30" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="G30" s="9">
+        <f t="array" ref="G30">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),6)),"")</f>
+        <v/>
+      </c>
+      <c r="H30" s="10">
+        <f t="array" ref="H30">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),6)),"")</f>
+        <v/>
+      </c>
+      <c r="J30" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="K30" s="9">
+        <f t="array" ref="K30">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),6)),"")</f>
+        <v/>
+      </c>
+      <c r="L30" s="10">
+        <f t="array" ref="L30">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),6)),"")</f>
+        <v/>
+      </c>
+      <c r="N30" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="O30" s="9">
+        <f t="array" ref="O30">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),6)),"")</f>
+        <v/>
+      </c>
+      <c r="P30" s="10">
+        <f t="array" ref="P30">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),6)),"")</f>
+        <v/>
+      </c>
+      <c r="R30" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="S30" s="9">
+        <f t="array" ref="S30">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),6)),"")</f>
+        <v/>
+      </c>
+      <c r="T30" s="10">
+        <f t="array" ref="T30">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),6)),"")</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5">
-        <f t="array" ref="A31">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A31))),"")</f>
-        <v/>
-      </c>
-      <c r="B31" s="6">
-        <f t="array" ref="B31">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A31))),"")</f>
+      <c r="B31" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C31" s="5">
+        <f t="array" ref="C31">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),7)),"")</f>
+        <v/>
+      </c>
+      <c r="D31" s="6">
+        <f t="array" ref="D31">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),7)),"")</f>
+        <v/>
+      </c>
+      <c r="F31" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="G31" s="5">
+        <f t="array" ref="G31">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),7)),"")</f>
+        <v/>
+      </c>
+      <c r="H31" s="6">
+        <f t="array" ref="H31">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),7)),"")</f>
+        <v/>
+      </c>
+      <c r="J31" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="K31" s="5">
+        <f t="array" ref="K31">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),7)),"")</f>
+        <v/>
+      </c>
+      <c r="L31" s="6">
+        <f t="array" ref="L31">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),7)),"")</f>
+        <v/>
+      </c>
+      <c r="N31" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="O31" s="5">
+        <f t="array" ref="O31">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),7)),"")</f>
+        <v/>
+      </c>
+      <c r="P31" s="6">
+        <f t="array" ref="P31">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),7)),"")</f>
+        <v/>
+      </c>
+      <c r="R31" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="S31" s="5">
+        <f t="array" ref="S31">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),7)),"")</f>
+        <v/>
+      </c>
+      <c r="T31" s="6">
+        <f t="array" ref="T31">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),7)),"")</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="9">
-        <f t="array" ref="A32">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A32))),"")</f>
-        <v/>
-      </c>
-      <c r="B32" s="10">
-        <f t="array" ref="B32">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A32))),"")</f>
+      <c r="B32" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="C32" s="9">
+        <f t="array" ref="C32">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),8)),"")</f>
+        <v/>
+      </c>
+      <c r="D32" s="10">
+        <f t="array" ref="D32">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),8)),"")</f>
+        <v/>
+      </c>
+      <c r="F32" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="G32" s="9">
+        <f t="array" ref="G32">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),8)),"")</f>
+        <v/>
+      </c>
+      <c r="H32" s="10">
+        <f t="array" ref="H32">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),8)),"")</f>
+        <v/>
+      </c>
+      <c r="J32" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="K32" s="9">
+        <f t="array" ref="K32">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),8)),"")</f>
+        <v/>
+      </c>
+      <c r="L32" s="10">
+        <f t="array" ref="L32">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),8)),"")</f>
+        <v/>
+      </c>
+      <c r="N32" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="O32" s="9">
+        <f t="array" ref="O32">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),8)),"")</f>
+        <v/>
+      </c>
+      <c r="P32" s="10">
+        <f t="array" ref="P32">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),8)),"")</f>
+        <v/>
+      </c>
+      <c r="R32" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="S32" s="9">
+        <f t="array" ref="S32">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),8)),"")</f>
+        <v/>
+      </c>
+      <c r="T32" s="10">
+        <f t="array" ref="T32">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),8)),"")</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5">
-        <f t="array" ref="A33">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A33))),"")</f>
-        <v/>
-      </c>
-      <c r="B33" s="6">
-        <f t="array" ref="B33">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A33))),"")</f>
+      <c r="B33" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="C33" s="5">
+        <f t="array" ref="C33">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),9)),"")</f>
+        <v/>
+      </c>
+      <c r="D33" s="6">
+        <f t="array" ref="D33">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),9)),"")</f>
+        <v/>
+      </c>
+      <c r="F33" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="G33" s="5">
+        <f t="array" ref="G33">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),9)),"")</f>
+        <v/>
+      </c>
+      <c r="H33" s="6">
+        <f t="array" ref="H33">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),9)),"")</f>
+        <v/>
+      </c>
+      <c r="J33" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="K33" s="5">
+        <f t="array" ref="K33">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),9)),"")</f>
+        <v/>
+      </c>
+      <c r="L33" s="6">
+        <f t="array" ref="L33">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),9)),"")</f>
+        <v/>
+      </c>
+      <c r="N33" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="O33" s="5">
+        <f t="array" ref="O33">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),9)),"")</f>
+        <v/>
+      </c>
+      <c r="P33" s="6">
+        <f t="array" ref="P33">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),9)),"")</f>
+        <v/>
+      </c>
+      <c r="R33" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="S33" s="5">
+        <f t="array" ref="S33">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),9)),"")</f>
+        <v/>
+      </c>
+      <c r="T33" s="6">
+        <f t="array" ref="T33">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),9)),"")</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="9">
-        <f t="array" ref="A34">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A34))),"")</f>
-        <v/>
-      </c>
-      <c r="B34" s="10">
-        <f t="array" ref="B34">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A34))),"")</f>
+      <c r="B34" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C34" s="9">
+        <f t="array" ref="C34">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),10)),"")</f>
+        <v/>
+      </c>
+      <c r="D34" s="10">
+        <f t="array" ref="D34">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),10)),"")</f>
+        <v/>
+      </c>
+      <c r="F34" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="G34" s="9">
+        <f t="array" ref="G34">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),10)),"")</f>
+        <v/>
+      </c>
+      <c r="H34" s="10">
+        <f t="array" ref="H34">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),10)),"")</f>
+        <v/>
+      </c>
+      <c r="J34" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="K34" s="9">
+        <f t="array" ref="K34">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),10)),"")</f>
+        <v/>
+      </c>
+      <c r="L34" s="10">
+        <f t="array" ref="L34">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),10)),"")</f>
+        <v/>
+      </c>
+      <c r="N34" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="O34" s="9">
+        <f t="array" ref="O34">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),10)),"")</f>
+        <v/>
+      </c>
+      <c r="P34" s="10">
+        <f t="array" ref="P34">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),10)),"")</f>
+        <v/>
+      </c>
+      <c r="R34" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="S34" s="9">
+        <f t="array" ref="S34">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),10)),"")</f>
+        <v/>
+      </c>
+      <c r="T34" s="10">
+        <f t="array" ref="T34">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),10)),"")</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5">
-        <f t="array" ref="A35">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A35))),"")</f>
-        <v/>
-      </c>
-      <c r="B35" s="6">
-        <f t="array" ref="B35">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A35))),"")</f>
+      <c r="B35" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="C35" s="5">
+        <f t="array" ref="C35">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),11)),"")</f>
+        <v/>
+      </c>
+      <c r="D35" s="6">
+        <f t="array" ref="D35">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),11)),"")</f>
+        <v/>
+      </c>
+      <c r="F35" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="G35" s="5">
+        <f t="array" ref="G35">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),11)),"")</f>
+        <v/>
+      </c>
+      <c r="H35" s="6">
+        <f t="array" ref="H35">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),11)),"")</f>
+        <v/>
+      </c>
+      <c r="J35" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="K35" s="5">
+        <f t="array" ref="K35">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),11)),"")</f>
+        <v/>
+      </c>
+      <c r="L35" s="6">
+        <f t="array" ref="L35">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),11)),"")</f>
+        <v/>
+      </c>
+      <c r="N35" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="O35" s="5">
+        <f t="array" ref="O35">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),11)),"")</f>
+        <v/>
+      </c>
+      <c r="P35" s="6">
+        <f t="array" ref="P35">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),11)),"")</f>
+        <v/>
+      </c>
+      <c r="R35" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="S35" s="5">
+        <f t="array" ref="S35">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),11)),"")</f>
+        <v/>
+      </c>
+      <c r="T35" s="6">
+        <f t="array" ref="T35">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),11)),"")</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="9">
-        <f t="array" ref="A36">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A36))),"")</f>
-        <v/>
-      </c>
-      <c r="B36" s="10">
-        <f t="array" ref="B36">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A36))),"")</f>
+      <c r="B36" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="C36" s="9">
+        <f t="array" ref="C36">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),12)),"")</f>
+        <v/>
+      </c>
+      <c r="D36" s="10">
+        <f t="array" ref="D36">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),12)),"")</f>
+        <v/>
+      </c>
+      <c r="F36" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="G36" s="9">
+        <f t="array" ref="G36">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),12)),"")</f>
+        <v/>
+      </c>
+      <c r="H36" s="10">
+        <f t="array" ref="H36">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),12)),"")</f>
+        <v/>
+      </c>
+      <c r="J36" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="K36" s="9">
+        <f t="array" ref="K36">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),12)),"")</f>
+        <v/>
+      </c>
+      <c r="L36" s="10">
+        <f t="array" ref="L36">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),12)),"")</f>
+        <v/>
+      </c>
+      <c r="N36" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="O36" s="9">
+        <f t="array" ref="O36">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),12)),"")</f>
+        <v/>
+      </c>
+      <c r="P36" s="10">
+        <f t="array" ref="P36">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),12)),"")</f>
+        <v/>
+      </c>
+      <c r="R36" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="S36" s="9">
+        <f t="array" ref="S36">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),12)),"")</f>
+        <v/>
+      </c>
+      <c r="T36" s="10">
+        <f t="array" ref="T36">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),12)),"")</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5">
-        <f t="array" ref="A37">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A37))),"")</f>
-        <v/>
-      </c>
-      <c r="B37" s="6">
-        <f t="array" ref="B37">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A37))),"")</f>
+      <c r="B37" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="C37" s="5">
+        <f t="array" ref="C37">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),13)),"")</f>
+        <v/>
+      </c>
+      <c r="D37" s="6">
+        <f t="array" ref="D37">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),13)),"")</f>
+        <v/>
+      </c>
+      <c r="F37" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="G37" s="5">
+        <f t="array" ref="G37">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),13)),"")</f>
+        <v/>
+      </c>
+      <c r="H37" s="6">
+        <f t="array" ref="H37">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),13)),"")</f>
+        <v/>
+      </c>
+      <c r="J37" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="K37" s="5">
+        <f t="array" ref="K37">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),13)),"")</f>
+        <v/>
+      </c>
+      <c r="L37" s="6">
+        <f t="array" ref="L37">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),13)),"")</f>
+        <v/>
+      </c>
+      <c r="N37" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="O37" s="5">
+        <f t="array" ref="O37">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),13)),"")</f>
+        <v/>
+      </c>
+      <c r="P37" s="6">
+        <f t="array" ref="P37">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),13)),"")</f>
+        <v/>
+      </c>
+      <c r="R37" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="S37" s="5">
+        <f t="array" ref="S37">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),13)),"")</f>
+        <v/>
+      </c>
+      <c r="T37" s="6">
+        <f t="array" ref="T37">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),13)),"")</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="9">
-        <f t="array" ref="A38">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A38))),"")</f>
-        <v/>
-      </c>
-      <c r="B38" s="10">
-        <f t="array" ref="B38">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A38))),"")</f>
+      <c r="B38" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="C38" s="9">
+        <f t="array" ref="C38">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),14)),"")</f>
+        <v/>
+      </c>
+      <c r="D38" s="10">
+        <f t="array" ref="D38">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),14)),"")</f>
+        <v/>
+      </c>
+      <c r="F38" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="G38" s="9">
+        <f t="array" ref="G38">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),14)),"")</f>
+        <v/>
+      </c>
+      <c r="H38" s="10">
+        <f t="array" ref="H38">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),14)),"")</f>
+        <v/>
+      </c>
+      <c r="J38" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="K38" s="9">
+        <f t="array" ref="K38">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),14)),"")</f>
+        <v/>
+      </c>
+      <c r="L38" s="10">
+        <f t="array" ref="L38">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),14)),"")</f>
+        <v/>
+      </c>
+      <c r="N38" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="O38" s="9">
+        <f t="array" ref="O38">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),14)),"")</f>
+        <v/>
+      </c>
+      <c r="P38" s="10">
+        <f t="array" ref="P38">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),14)),"")</f>
+        <v/>
+      </c>
+      <c r="R38" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="S38" s="9">
+        <f t="array" ref="S38">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),14)),"")</f>
+        <v/>
+      </c>
+      <c r="T38" s="10">
+        <f t="array" ref="T38">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),14)),"")</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5">
-        <f t="array" ref="A39">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A39))),"")</f>
-        <v/>
-      </c>
-      <c r="B39" s="6">
-        <f t="array" ref="B39">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A39))),"")</f>
+      <c r="B39" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="C39" s="5">
+        <f t="array" ref="C39">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),15)),"")</f>
+        <v/>
+      </c>
+      <c r="D39" s="6">
+        <f t="array" ref="D39">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),15)),"")</f>
+        <v/>
+      </c>
+      <c r="F39" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="G39" s="5">
+        <f t="array" ref="G39">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),15)),"")</f>
+        <v/>
+      </c>
+      <c r="H39" s="6">
+        <f t="array" ref="H39">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),15)),"")</f>
+        <v/>
+      </c>
+      <c r="J39" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="K39" s="5">
+        <f t="array" ref="K39">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),15)),"")</f>
+        <v/>
+      </c>
+      <c r="L39" s="6">
+        <f t="array" ref="L39">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),15)),"")</f>
+        <v/>
+      </c>
+      <c r="N39" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="O39" s="5">
+        <f t="array" ref="O39">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),15)),"")</f>
+        <v/>
+      </c>
+      <c r="P39" s="6">
+        <f t="array" ref="P39">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),15)),"")</f>
+        <v/>
+      </c>
+      <c r="R39" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="S39" s="5">
+        <f t="array" ref="S39">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),15)),"")</f>
+        <v/>
+      </c>
+      <c r="T39" s="6">
+        <f t="array" ref="T39">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$23,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),15)),"")</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="9">
-        <f t="array" ref="A40">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A40))),"")</f>
-        <v/>
-      </c>
-      <c r="B40" s="10">
-        <f t="array" ref="B40">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A40))),"")</f>
+      <c r="B40" s="17" t="inlineStr">
+        <is>
+          <t>Total Amount Spent</t>
+        </is>
+      </c>
+      <c r="D40" s="18">
+        <f>Balance!$C$9</f>
+        <v/>
+      </c>
+      <c r="F40" s="17" t="inlineStr">
+        <is>
+          <t>Total Amount Spent</t>
+        </is>
+      </c>
+      <c r="H40" s="18">
+        <f>Balance!$C$10</f>
+        <v/>
+      </c>
+      <c r="J40" s="17" t="inlineStr">
+        <is>
+          <t>Total Amount Spent</t>
+        </is>
+      </c>
+      <c r="L40" s="18">
+        <f>Balance!$C$11</f>
+        <v/>
+      </c>
+      <c r="N40" s="17" t="inlineStr">
+        <is>
+          <t>Total Amount Spent</t>
+        </is>
+      </c>
+      <c r="P40" s="18">
+        <f>Balance!$C$12</f>
+        <v/>
+      </c>
+      <c r="R40" s="17" t="inlineStr">
+        <is>
+          <t>Total Amount Spent</t>
+        </is>
+      </c>
+      <c r="T40" s="18">
+        <f>Balance!$C$13</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5">
-        <f t="array" ref="A41">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A41))),"")</f>
-        <v/>
-      </c>
-      <c r="B41" s="6">
-        <f t="array" ref="B41">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A41))),"")</f>
+      <c r="B41" s="19" t="inlineStr">
+        <is>
+          <t>Total Amount Left</t>
+        </is>
+      </c>
+      <c r="D41" s="20">
+        <f>Balance!$D$9</f>
+        <v/>
+      </c>
+      <c r="F41" s="19" t="inlineStr">
+        <is>
+          <t>Total Amount Left</t>
+        </is>
+      </c>
+      <c r="H41" s="20">
+        <f>Balance!$D$10</f>
+        <v/>
+      </c>
+      <c r="J41" s="19" t="inlineStr">
+        <is>
+          <t>Total Amount Left</t>
+        </is>
+      </c>
+      <c r="L41" s="20">
+        <f>Balance!$D$11</f>
+        <v/>
+      </c>
+      <c r="N41" s="19" t="inlineStr">
+        <is>
+          <t>Total Amount Left</t>
+        </is>
+      </c>
+      <c r="P41" s="20">
+        <f>Balance!$D$12</f>
+        <v/>
+      </c>
+      <c r="R41" s="19" t="inlineStr">
+        <is>
+          <t>Total Amount Left</t>
+        </is>
+      </c>
+      <c r="T41" s="20">
+        <f>Balance!$D$13</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="9">
-        <f t="array" ref="A42">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A42))),"")</f>
-        <v/>
-      </c>
-      <c r="B42" s="10">
-        <f t="array" ref="B42">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A42))),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5">
-        <f t="array" ref="A43">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A43))),"")</f>
-        <v/>
-      </c>
-      <c r="B43" s="6">
-        <f t="array" ref="B43">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A43))),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="9">
-        <f t="array" ref="A44">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A44))),"")</f>
-        <v/>
-      </c>
-      <c r="B44" s="10">
-        <f t="array" ref="B44">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A44))),"")</f>
+      <c r="B42" s="21" t="inlineStr">
+        <is>
+          <t>Total Amount</t>
+        </is>
+      </c>
+      <c r="D42" s="14">
+        <f>Balance!$B$9</f>
+        <v/>
+      </c>
+      <c r="F42" s="21" t="inlineStr">
+        <is>
+          <t>Total Amount</t>
+        </is>
+      </c>
+      <c r="H42" s="14">
+        <f>Balance!$B$10</f>
+        <v/>
+      </c>
+      <c r="J42" s="21" t="inlineStr">
+        <is>
+          <t>Total Amount</t>
+        </is>
+      </c>
+      <c r="L42" s="14">
+        <f>Balance!$B$11</f>
+        <v/>
+      </c>
+      <c r="N42" s="21" t="inlineStr">
+        <is>
+          <t>Total Amount</t>
+        </is>
+      </c>
+      <c r="P42" s="14">
+        <f>Balance!$B$12</f>
+        <v/>
+      </c>
+      <c r="R42" s="21" t="inlineStr">
+        <is>
+          <t>Total Amount</t>
+        </is>
+      </c>
+      <c r="T42" s="14">
+        <f>Balance!$B$13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="B44" s="16">
+        <f>Balance!$A$14</f>
+        <v/>
+      </c>
+      <c r="F44" s="16">
+        <f>Balance!$A$15</f>
+        <v/>
+      </c>
+      <c r="J44" s="16">
+        <f>Balance!$A$16</f>
+        <v/>
+      </c>
+      <c r="N44" s="16">
+        <f>Balance!$A$17</f>
+        <v/>
+      </c>
+      <c r="R44" s="16">
+        <f>Balance!$A$18</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5">
-        <f t="array" ref="A45">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A45))),"")</f>
-        <v/>
-      </c>
-      <c r="B45" s="6">
-        <f t="array" ref="B45">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A45))),"")</f>
-        <v/>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>S.No</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Player Name</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>S.No</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>Player Name</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>S.No</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>Player Name</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t>S.No</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t>Player Name</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="R45" s="3" t="inlineStr">
+        <is>
+          <t>S.No</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="inlineStr">
+        <is>
+          <t>Player Name</t>
+        </is>
+      </c>
+      <c r="T45" s="3" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="9">
-        <f t="array" ref="A46">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A46))),"")</f>
-        <v/>
-      </c>
-      <c r="B46" s="10">
-        <f t="array" ref="B46">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A46))),"")</f>
+      <c r="B46" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" s="5">
+        <f t="array" ref="C46">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),1)),"")</f>
+        <v/>
+      </c>
+      <c r="D46" s="6">
+        <f t="array" ref="D46">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),1)),"")</f>
+        <v/>
+      </c>
+      <c r="F46" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="5">
+        <f t="array" ref="G46">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),1)),"")</f>
+        <v/>
+      </c>
+      <c r="H46" s="6">
+        <f t="array" ref="H46">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),1)),"")</f>
+        <v/>
+      </c>
+      <c r="J46" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K46" s="5">
+        <f t="array" ref="K46">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),1)),"")</f>
+        <v/>
+      </c>
+      <c r="L46" s="6">
+        <f t="array" ref="L46">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),1)),"")</f>
+        <v/>
+      </c>
+      <c r="N46" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O46" s="5">
+        <f t="array" ref="O46">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),1)),"")</f>
+        <v/>
+      </c>
+      <c r="P46" s="6">
+        <f t="array" ref="P46">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),1)),"")</f>
+        <v/>
+      </c>
+      <c r="R46" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S46" s="5">
+        <f t="array" ref="S46">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),1)),"")</f>
+        <v/>
+      </c>
+      <c r="T46" s="6">
+        <f t="array" ref="T46">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),1)),"")</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5">
-        <f t="array" ref="A47">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A47))),"")</f>
-        <v/>
-      </c>
-      <c r="B47" s="6">
-        <f t="array" ref="B47">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A47))),"")</f>
+      <c r="B47" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C47" s="9">
+        <f t="array" ref="C47">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),2)),"")</f>
+        <v/>
+      </c>
+      <c r="D47" s="10">
+        <f t="array" ref="D47">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),2)),"")</f>
+        <v/>
+      </c>
+      <c r="F47" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G47" s="9">
+        <f t="array" ref="G47">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),2)),"")</f>
+        <v/>
+      </c>
+      <c r="H47" s="10">
+        <f t="array" ref="H47">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),2)),"")</f>
+        <v/>
+      </c>
+      <c r="J47" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K47" s="9">
+        <f t="array" ref="K47">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),2)),"")</f>
+        <v/>
+      </c>
+      <c r="L47" s="10">
+        <f t="array" ref="L47">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),2)),"")</f>
+        <v/>
+      </c>
+      <c r="N47" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="O47" s="9">
+        <f t="array" ref="O47">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),2)),"")</f>
+        <v/>
+      </c>
+      <c r="P47" s="10">
+        <f t="array" ref="P47">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),2)),"")</f>
+        <v/>
+      </c>
+      <c r="R47" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="S47" s="9">
+        <f t="array" ref="S47">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),2)),"")</f>
+        <v/>
+      </c>
+      <c r="T47" s="10">
+        <f t="array" ref="T47">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),2)),"")</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="9">
-        <f t="array" ref="A48">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A48))),"")</f>
-        <v/>
-      </c>
-      <c r="B48" s="10">
-        <f t="array" ref="B48">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$A$1,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),ROWS($A$9:A48))),"")</f>
+      <c r="B48" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C48" s="5">
+        <f t="array" ref="C48">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),3)),"")</f>
+        <v/>
+      </c>
+      <c r="D48" s="6">
+        <f t="array" ref="D48">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),3)),"")</f>
+        <v/>
+      </c>
+      <c r="F48" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G48" s="5">
+        <f t="array" ref="G48">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),3)),"")</f>
+        <v/>
+      </c>
+      <c r="H48" s="6">
+        <f t="array" ref="H48">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),3)),"")</f>
+        <v/>
+      </c>
+      <c r="J48" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K48" s="5">
+        <f t="array" ref="K48">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),3)),"")</f>
+        <v/>
+      </c>
+      <c r="L48" s="6">
+        <f t="array" ref="L48">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),3)),"")</f>
+        <v/>
+      </c>
+      <c r="N48" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="O48" s="5">
+        <f t="array" ref="O48">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),3)),"")</f>
+        <v/>
+      </c>
+      <c r="P48" s="6">
+        <f t="array" ref="P48">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),3)),"")</f>
+        <v/>
+      </c>
+      <c r="R48" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="S48" s="5">
+        <f t="array" ref="S48">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),3)),"")</f>
+        <v/>
+      </c>
+      <c r="T48" s="6">
+        <f t="array" ref="T48">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),3)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C49" s="9">
+        <f t="array" ref="C49">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),4)),"")</f>
+        <v/>
+      </c>
+      <c r="D49" s="10">
+        <f t="array" ref="D49">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),4)),"")</f>
+        <v/>
+      </c>
+      <c r="F49" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="G49" s="9">
+        <f t="array" ref="G49">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),4)),"")</f>
+        <v/>
+      </c>
+      <c r="H49" s="10">
+        <f t="array" ref="H49">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),4)),"")</f>
+        <v/>
+      </c>
+      <c r="J49" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K49" s="9">
+        <f t="array" ref="K49">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),4)),"")</f>
+        <v/>
+      </c>
+      <c r="L49" s="10">
+        <f t="array" ref="L49">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),4)),"")</f>
+        <v/>
+      </c>
+      <c r="N49" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="O49" s="9">
+        <f t="array" ref="O49">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),4)),"")</f>
+        <v/>
+      </c>
+      <c r="P49" s="10">
+        <f t="array" ref="P49">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),4)),"")</f>
+        <v/>
+      </c>
+      <c r="R49" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="S49" s="9">
+        <f t="array" ref="S49">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),4)),"")</f>
+        <v/>
+      </c>
+      <c r="T49" s="10">
+        <f t="array" ref="T49">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),4)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C50" s="5">
+        <f t="array" ref="C50">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),5)),"")</f>
+        <v/>
+      </c>
+      <c r="D50" s="6">
+        <f t="array" ref="D50">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),5)),"")</f>
+        <v/>
+      </c>
+      <c r="F50" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G50" s="5">
+        <f t="array" ref="G50">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),5)),"")</f>
+        <v/>
+      </c>
+      <c r="H50" s="6">
+        <f t="array" ref="H50">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),5)),"")</f>
+        <v/>
+      </c>
+      <c r="J50" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K50" s="5">
+        <f t="array" ref="K50">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),5)),"")</f>
+        <v/>
+      </c>
+      <c r="L50" s="6">
+        <f t="array" ref="L50">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),5)),"")</f>
+        <v/>
+      </c>
+      <c r="N50" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="O50" s="5">
+        <f t="array" ref="O50">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),5)),"")</f>
+        <v/>
+      </c>
+      <c r="P50" s="6">
+        <f t="array" ref="P50">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),5)),"")</f>
+        <v/>
+      </c>
+      <c r="R50" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="S50" s="5">
+        <f t="array" ref="S50">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),5)),"")</f>
+        <v/>
+      </c>
+      <c r="T50" s="6">
+        <f t="array" ref="T50">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),5)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C51" s="9">
+        <f t="array" ref="C51">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),6)),"")</f>
+        <v/>
+      </c>
+      <c r="D51" s="10">
+        <f t="array" ref="D51">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),6)),"")</f>
+        <v/>
+      </c>
+      <c r="F51" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="G51" s="9">
+        <f t="array" ref="G51">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),6)),"")</f>
+        <v/>
+      </c>
+      <c r="H51" s="10">
+        <f t="array" ref="H51">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),6)),"")</f>
+        <v/>
+      </c>
+      <c r="J51" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="K51" s="9">
+        <f t="array" ref="K51">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),6)),"")</f>
+        <v/>
+      </c>
+      <c r="L51" s="10">
+        <f t="array" ref="L51">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),6)),"")</f>
+        <v/>
+      </c>
+      <c r="N51" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="O51" s="9">
+        <f t="array" ref="O51">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),6)),"")</f>
+        <v/>
+      </c>
+      <c r="P51" s="10">
+        <f t="array" ref="P51">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),6)),"")</f>
+        <v/>
+      </c>
+      <c r="R51" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="S51" s="9">
+        <f t="array" ref="S51">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),6)),"")</f>
+        <v/>
+      </c>
+      <c r="T51" s="10">
+        <f t="array" ref="T51">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),6)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C52" s="5">
+        <f t="array" ref="C52">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),7)),"")</f>
+        <v/>
+      </c>
+      <c r="D52" s="6">
+        <f t="array" ref="D52">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),7)),"")</f>
+        <v/>
+      </c>
+      <c r="F52" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="G52" s="5">
+        <f t="array" ref="G52">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),7)),"")</f>
+        <v/>
+      </c>
+      <c r="H52" s="6">
+        <f t="array" ref="H52">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),7)),"")</f>
+        <v/>
+      </c>
+      <c r="J52" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="K52" s="5">
+        <f t="array" ref="K52">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),7)),"")</f>
+        <v/>
+      </c>
+      <c r="L52" s="6">
+        <f t="array" ref="L52">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),7)),"")</f>
+        <v/>
+      </c>
+      <c r="N52" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="O52" s="5">
+        <f t="array" ref="O52">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),7)),"")</f>
+        <v/>
+      </c>
+      <c r="P52" s="6">
+        <f t="array" ref="P52">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),7)),"")</f>
+        <v/>
+      </c>
+      <c r="R52" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="S52" s="5">
+        <f t="array" ref="S52">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),7)),"")</f>
+        <v/>
+      </c>
+      <c r="T52" s="6">
+        <f t="array" ref="T52">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),7)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="C53" s="9">
+        <f t="array" ref="C53">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),8)),"")</f>
+        <v/>
+      </c>
+      <c r="D53" s="10">
+        <f t="array" ref="D53">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),8)),"")</f>
+        <v/>
+      </c>
+      <c r="F53" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="G53" s="9">
+        <f t="array" ref="G53">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),8)),"")</f>
+        <v/>
+      </c>
+      <c r="H53" s="10">
+        <f t="array" ref="H53">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),8)),"")</f>
+        <v/>
+      </c>
+      <c r="J53" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="K53" s="9">
+        <f t="array" ref="K53">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),8)),"")</f>
+        <v/>
+      </c>
+      <c r="L53" s="10">
+        <f t="array" ref="L53">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),8)),"")</f>
+        <v/>
+      </c>
+      <c r="N53" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="O53" s="9">
+        <f t="array" ref="O53">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),8)),"")</f>
+        <v/>
+      </c>
+      <c r="P53" s="10">
+        <f t="array" ref="P53">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),8)),"")</f>
+        <v/>
+      </c>
+      <c r="R53" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="S53" s="9">
+        <f t="array" ref="S53">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),8)),"")</f>
+        <v/>
+      </c>
+      <c r="T53" s="10">
+        <f t="array" ref="T53">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),8)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="C54" s="5">
+        <f t="array" ref="C54">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),9)),"")</f>
+        <v/>
+      </c>
+      <c r="D54" s="6">
+        <f t="array" ref="D54">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),9)),"")</f>
+        <v/>
+      </c>
+      <c r="F54" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="G54" s="5">
+        <f t="array" ref="G54">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),9)),"")</f>
+        <v/>
+      </c>
+      <c r="H54" s="6">
+        <f t="array" ref="H54">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),9)),"")</f>
+        <v/>
+      </c>
+      <c r="J54" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="K54" s="5">
+        <f t="array" ref="K54">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),9)),"")</f>
+        <v/>
+      </c>
+      <c r="L54" s="6">
+        <f t="array" ref="L54">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),9)),"")</f>
+        <v/>
+      </c>
+      <c r="N54" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="O54" s="5">
+        <f t="array" ref="O54">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),9)),"")</f>
+        <v/>
+      </c>
+      <c r="P54" s="6">
+        <f t="array" ref="P54">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),9)),"")</f>
+        <v/>
+      </c>
+      <c r="R54" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="S54" s="5">
+        <f t="array" ref="S54">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),9)),"")</f>
+        <v/>
+      </c>
+      <c r="T54" s="6">
+        <f t="array" ref="T54">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),9)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C55" s="9">
+        <f t="array" ref="C55">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),10)),"")</f>
+        <v/>
+      </c>
+      <c r="D55" s="10">
+        <f t="array" ref="D55">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),10)),"")</f>
+        <v/>
+      </c>
+      <c r="F55" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="G55" s="9">
+        <f t="array" ref="G55">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),10)),"")</f>
+        <v/>
+      </c>
+      <c r="H55" s="10">
+        <f t="array" ref="H55">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),10)),"")</f>
+        <v/>
+      </c>
+      <c r="J55" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="K55" s="9">
+        <f t="array" ref="K55">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),10)),"")</f>
+        <v/>
+      </c>
+      <c r="L55" s="10">
+        <f t="array" ref="L55">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),10)),"")</f>
+        <v/>
+      </c>
+      <c r="N55" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="O55" s="9">
+        <f t="array" ref="O55">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),10)),"")</f>
+        <v/>
+      </c>
+      <c r="P55" s="10">
+        <f t="array" ref="P55">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),10)),"")</f>
+        <v/>
+      </c>
+      <c r="R55" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="S55" s="9">
+        <f t="array" ref="S55">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),10)),"")</f>
+        <v/>
+      </c>
+      <c r="T55" s="10">
+        <f t="array" ref="T55">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),10)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="C56" s="5">
+        <f t="array" ref="C56">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),11)),"")</f>
+        <v/>
+      </c>
+      <c r="D56" s="6">
+        <f t="array" ref="D56">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),11)),"")</f>
+        <v/>
+      </c>
+      <c r="F56" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="G56" s="5">
+        <f t="array" ref="G56">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),11)),"")</f>
+        <v/>
+      </c>
+      <c r="H56" s="6">
+        <f t="array" ref="H56">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),11)),"")</f>
+        <v/>
+      </c>
+      <c r="J56" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="K56" s="5">
+        <f t="array" ref="K56">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),11)),"")</f>
+        <v/>
+      </c>
+      <c r="L56" s="6">
+        <f t="array" ref="L56">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),11)),"")</f>
+        <v/>
+      </c>
+      <c r="N56" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="O56" s="5">
+        <f t="array" ref="O56">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),11)),"")</f>
+        <v/>
+      </c>
+      <c r="P56" s="6">
+        <f t="array" ref="P56">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),11)),"")</f>
+        <v/>
+      </c>
+      <c r="R56" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="S56" s="5">
+        <f t="array" ref="S56">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),11)),"")</f>
+        <v/>
+      </c>
+      <c r="T56" s="6">
+        <f t="array" ref="T56">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),11)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="C57" s="9">
+        <f t="array" ref="C57">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),12)),"")</f>
+        <v/>
+      </c>
+      <c r="D57" s="10">
+        <f t="array" ref="D57">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),12)),"")</f>
+        <v/>
+      </c>
+      <c r="F57" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="G57" s="9">
+        <f t="array" ref="G57">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),12)),"")</f>
+        <v/>
+      </c>
+      <c r="H57" s="10">
+        <f t="array" ref="H57">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),12)),"")</f>
+        <v/>
+      </c>
+      <c r="J57" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="K57" s="9">
+        <f t="array" ref="K57">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),12)),"")</f>
+        <v/>
+      </c>
+      <c r="L57" s="10">
+        <f t="array" ref="L57">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),12)),"")</f>
+        <v/>
+      </c>
+      <c r="N57" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="O57" s="9">
+        <f t="array" ref="O57">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),12)),"")</f>
+        <v/>
+      </c>
+      <c r="P57" s="10">
+        <f t="array" ref="P57">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),12)),"")</f>
+        <v/>
+      </c>
+      <c r="R57" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="S57" s="9">
+        <f t="array" ref="S57">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),12)),"")</f>
+        <v/>
+      </c>
+      <c r="T57" s="10">
+        <f t="array" ref="T57">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),12)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="C58" s="5">
+        <f t="array" ref="C58">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),13)),"")</f>
+        <v/>
+      </c>
+      <c r="D58" s="6">
+        <f t="array" ref="D58">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),13)),"")</f>
+        <v/>
+      </c>
+      <c r="F58" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="G58" s="5">
+        <f t="array" ref="G58">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),13)),"")</f>
+        <v/>
+      </c>
+      <c r="H58" s="6">
+        <f t="array" ref="H58">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),13)),"")</f>
+        <v/>
+      </c>
+      <c r="J58" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="K58" s="5">
+        <f t="array" ref="K58">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),13)),"")</f>
+        <v/>
+      </c>
+      <c r="L58" s="6">
+        <f t="array" ref="L58">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),13)),"")</f>
+        <v/>
+      </c>
+      <c r="N58" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="O58" s="5">
+        <f t="array" ref="O58">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),13)),"")</f>
+        <v/>
+      </c>
+      <c r="P58" s="6">
+        <f t="array" ref="P58">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),13)),"")</f>
+        <v/>
+      </c>
+      <c r="R58" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="S58" s="5">
+        <f t="array" ref="S58">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),13)),"")</f>
+        <v/>
+      </c>
+      <c r="T58" s="6">
+        <f t="array" ref="T58">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),13)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="C59" s="9">
+        <f t="array" ref="C59">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),14)),"")</f>
+        <v/>
+      </c>
+      <c r="D59" s="10">
+        <f t="array" ref="D59">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),14)),"")</f>
+        <v/>
+      </c>
+      <c r="F59" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="G59" s="9">
+        <f t="array" ref="G59">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),14)),"")</f>
+        <v/>
+      </c>
+      <c r="H59" s="10">
+        <f t="array" ref="H59">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),14)),"")</f>
+        <v/>
+      </c>
+      <c r="J59" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="K59" s="9">
+        <f t="array" ref="K59">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),14)),"")</f>
+        <v/>
+      </c>
+      <c r="L59" s="10">
+        <f t="array" ref="L59">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),14)),"")</f>
+        <v/>
+      </c>
+      <c r="N59" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="O59" s="9">
+        <f t="array" ref="O59">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),14)),"")</f>
+        <v/>
+      </c>
+      <c r="P59" s="10">
+        <f t="array" ref="P59">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),14)),"")</f>
+        <v/>
+      </c>
+      <c r="R59" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="S59" s="9">
+        <f t="array" ref="S59">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),14)),"")</f>
+        <v/>
+      </c>
+      <c r="T59" s="10">
+        <f t="array" ref="T59">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),14)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="C60" s="5">
+        <f t="array" ref="C60">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),15)),"")</f>
+        <v/>
+      </c>
+      <c r="D60" s="6">
+        <f t="array" ref="D60">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$B$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),15)),"")</f>
+        <v/>
+      </c>
+      <c r="F60" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="G60" s="5">
+        <f t="array" ref="G60">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),15)),"")</f>
+        <v/>
+      </c>
+      <c r="H60" s="6">
+        <f t="array" ref="H60">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$F$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),15)),"")</f>
+        <v/>
+      </c>
+      <c r="J60" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="K60" s="5">
+        <f t="array" ref="K60">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),15)),"")</f>
+        <v/>
+      </c>
+      <c r="L60" s="6">
+        <f t="array" ref="L60">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$J$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),15)),"")</f>
+        <v/>
+      </c>
+      <c r="N60" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="O60" s="5">
+        <f t="array" ref="O60">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),15)),"")</f>
+        <v/>
+      </c>
+      <c r="P60" s="6">
+        <f t="array" ref="P60">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$N$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),15)),"")</f>
+        <v/>
+      </c>
+      <c r="R60" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="S60" s="5">
+        <f t="array" ref="S60">IFERROR(INDEX(Auction!$A$5:$A$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),15)),"")</f>
+        <v/>
+      </c>
+      <c r="T60" s="6">
+        <f t="array" ref="T60">IFERROR(INDEX(Auction!$B$5:$B$1000,SMALL(IF(Auction!$C$5:$C$1000=$R$44,ROW(Auction!$C$5:$C$1000)-ROW(Auction!$C$5)+1),15)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="17" t="inlineStr">
+        <is>
+          <t>Total Amount Spent</t>
+        </is>
+      </c>
+      <c r="D61" s="18">
+        <f>Balance!$C$14</f>
+        <v/>
+      </c>
+      <c r="F61" s="17" t="inlineStr">
+        <is>
+          <t>Total Amount Spent</t>
+        </is>
+      </c>
+      <c r="H61" s="18">
+        <f>Balance!$C$15</f>
+        <v/>
+      </c>
+      <c r="J61" s="17" t="inlineStr">
+        <is>
+          <t>Total Amount Spent</t>
+        </is>
+      </c>
+      <c r="L61" s="18">
+        <f>Balance!$C$16</f>
+        <v/>
+      </c>
+      <c r="N61" s="17" t="inlineStr">
+        <is>
+          <t>Total Amount Spent</t>
+        </is>
+      </c>
+      <c r="P61" s="18">
+        <f>Balance!$C$17</f>
+        <v/>
+      </c>
+      <c r="R61" s="17" t="inlineStr">
+        <is>
+          <t>Total Amount Spent</t>
+        </is>
+      </c>
+      <c r="T61" s="18">
+        <f>Balance!$C$18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="19" t="inlineStr">
+        <is>
+          <t>Total Amount Left</t>
+        </is>
+      </c>
+      <c r="D62" s="20">
+        <f>Balance!$D$14</f>
+        <v/>
+      </c>
+      <c r="F62" s="19" t="inlineStr">
+        <is>
+          <t>Total Amount Left</t>
+        </is>
+      </c>
+      <c r="H62" s="20">
+        <f>Balance!$D$15</f>
+        <v/>
+      </c>
+      <c r="J62" s="19" t="inlineStr">
+        <is>
+          <t>Total Amount Left</t>
+        </is>
+      </c>
+      <c r="L62" s="20">
+        <f>Balance!$D$16</f>
+        <v/>
+      </c>
+      <c r="N62" s="19" t="inlineStr">
+        <is>
+          <t>Total Amount Left</t>
+        </is>
+      </c>
+      <c r="P62" s="20">
+        <f>Balance!$D$17</f>
+        <v/>
+      </c>
+      <c r="R62" s="19" t="inlineStr">
+        <is>
+          <t>Total Amount Left</t>
+        </is>
+      </c>
+      <c r="T62" s="20">
+        <f>Balance!$D$18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="21" t="inlineStr">
+        <is>
+          <t>Total Amount</t>
+        </is>
+      </c>
+      <c r="D63" s="14">
+        <f>Balance!$B$14</f>
+        <v/>
+      </c>
+      <c r="F63" s="21" t="inlineStr">
+        <is>
+          <t>Total Amount</t>
+        </is>
+      </c>
+      <c r="H63" s="14">
+        <f>Balance!$B$15</f>
+        <v/>
+      </c>
+      <c r="J63" s="21" t="inlineStr">
+        <is>
+          <t>Total Amount</t>
+        </is>
+      </c>
+      <c r="L63" s="14">
+        <f>Balance!$B$16</f>
+        <v/>
+      </c>
+      <c r="N63" s="21" t="inlineStr">
+        <is>
+          <t>Total Amount</t>
+        </is>
+      </c>
+      <c r="P63" s="14">
+        <f>Balance!$B$17</f>
+        <v/>
+      </c>
+      <c r="R63" s="21" t="inlineStr">
+        <is>
+          <t>Total Amount</t>
+        </is>
+      </c>
+      <c r="T63" s="14">
+        <f>Balance!$B$18</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
+  <mergeCells count="60">
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="N20:O20"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="N63:O63"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="F63:G63"/>
+    <mergeCell ref="R63:S63"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="N41:O41"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="N44:P44"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="R40:S40"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="N21:O21"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="N42:O42"/>
+    <mergeCell ref="N62:O62"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="N61:O61"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="F62:G62"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="R42:S42"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="J63:K63"/>
+    <mergeCell ref="J23:L23"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="N19:O19"/>
+    <mergeCell ref="R23:T23"/>
+    <mergeCell ref="R41:S41"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="F44:H44"/>
+    <mergeCell ref="J44:L44"/>
+    <mergeCell ref="N40:O40"/>
+    <mergeCell ref="F61:G61"/>
+    <mergeCell ref="R44:T44"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="R62:S62"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="J62:K62"/>
+    <mergeCell ref="J42:K42"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="J61:K61"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="R61:S61"/>
+    <mergeCell ref="B2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11424,52 +14832,52 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="16">
-        <f>Balance!A5</f>
+      <c r="A1" s="22">
+        <f>Balance!A4</f>
         <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="17" t="inlineStr">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t>Purse (Cr)</t>
         </is>
       </c>
-      <c r="B3" s="18">
-        <f>Balance!B5</f>
+      <c r="B3" s="24">
+        <f>Balance!B4</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="23" t="inlineStr">
         <is>
           <t>Spent (Cr)</t>
         </is>
       </c>
-      <c r="B4" s="18">
-        <f>Balance!C5</f>
+      <c r="B4" s="24">
+        <f>Balance!C4</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Balance (Cr)</t>
         </is>
       </c>
-      <c r="B5" s="20">
-        <f>Balance!D5</f>
+      <c r="B5" s="26">
+        <f>Balance!D4</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="27" t="inlineStr">
         <is>
           <t>Players</t>
         </is>
       </c>
-      <c r="B6" s="22">
-        <f>Balance!E5</f>
+      <c r="B6" s="28">
+        <f>Balance!E4</f>
         <v/>
       </c>
     </row>
@@ -11908,52 +15316,52 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="16">
-        <f>Balance!A6</f>
+      <c r="A1" s="22">
+        <f>Balance!A5</f>
         <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="17" t="inlineStr">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t>Purse (Cr)</t>
         </is>
       </c>
-      <c r="B3" s="18">
-        <f>Balance!B6</f>
+      <c r="B3" s="24">
+        <f>Balance!B5</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="23" t="inlineStr">
         <is>
           <t>Spent (Cr)</t>
         </is>
       </c>
-      <c r="B4" s="18">
-        <f>Balance!C6</f>
+      <c r="B4" s="24">
+        <f>Balance!C5</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Balance (Cr)</t>
         </is>
       </c>
-      <c r="B5" s="20">
-        <f>Balance!D6</f>
+      <c r="B5" s="26">
+        <f>Balance!D5</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="27" t="inlineStr">
         <is>
           <t>Players</t>
         </is>
       </c>
-      <c r="B6" s="22">
-        <f>Balance!E6</f>
+      <c r="B6" s="28">
+        <f>Balance!E5</f>
         <v/>
       </c>
     </row>
@@ -12392,52 +15800,52 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="16">
-        <f>Balance!A7</f>
+      <c r="A1" s="22">
+        <f>Balance!A6</f>
         <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="17" t="inlineStr">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t>Purse (Cr)</t>
         </is>
       </c>
-      <c r="B3" s="18">
-        <f>Balance!B7</f>
+      <c r="B3" s="24">
+        <f>Balance!B6</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="23" t="inlineStr">
         <is>
           <t>Spent (Cr)</t>
         </is>
       </c>
-      <c r="B4" s="18">
-        <f>Balance!C7</f>
+      <c r="B4" s="24">
+        <f>Balance!C6</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Balance (Cr)</t>
         </is>
       </c>
-      <c r="B5" s="20">
-        <f>Balance!D7</f>
+      <c r="B5" s="26">
+        <f>Balance!D6</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="27" t="inlineStr">
         <is>
           <t>Players</t>
         </is>
       </c>
-      <c r="B6" s="22">
-        <f>Balance!E7</f>
+      <c r="B6" s="28">
+        <f>Balance!E6</f>
         <v/>
       </c>
     </row>
@@ -12876,52 +16284,52 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="16">
-        <f>Balance!A8</f>
+      <c r="A1" s="22">
+        <f>Balance!A7</f>
         <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="17" t="inlineStr">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t>Purse (Cr)</t>
         </is>
       </c>
-      <c r="B3" s="18">
-        <f>Balance!B8</f>
+      <c r="B3" s="24">
+        <f>Balance!B7</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="23" t="inlineStr">
         <is>
           <t>Spent (Cr)</t>
         </is>
       </c>
-      <c r="B4" s="18">
-        <f>Balance!C8</f>
+      <c r="B4" s="24">
+        <f>Balance!C7</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Balance (Cr)</t>
         </is>
       </c>
-      <c r="B5" s="20">
-        <f>Balance!D8</f>
+      <c r="B5" s="26">
+        <f>Balance!D7</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="27" t="inlineStr">
         <is>
           <t>Players</t>
         </is>
       </c>
-      <c r="B6" s="22">
-        <f>Balance!E8</f>
+      <c r="B6" s="28">
+        <f>Balance!E7</f>
         <v/>
       </c>
     </row>
@@ -13360,52 +16768,52 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="16">
-        <f>Balance!A9</f>
+      <c r="A1" s="22">
+        <f>Balance!A8</f>
         <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="17" t="inlineStr">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t>Purse (Cr)</t>
         </is>
       </c>
-      <c r="B3" s="18">
-        <f>Balance!B9</f>
+      <c r="B3" s="24">
+        <f>Balance!B8</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="23" t="inlineStr">
         <is>
           <t>Spent (Cr)</t>
         </is>
       </c>
-      <c r="B4" s="18">
-        <f>Balance!C9</f>
+      <c r="B4" s="24">
+        <f>Balance!C8</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Balance (Cr)</t>
         </is>
       </c>
-      <c r="B5" s="20">
-        <f>Balance!D9</f>
+      <c r="B5" s="26">
+        <f>Balance!D8</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="27" t="inlineStr">
         <is>
           <t>Players</t>
         </is>
       </c>
-      <c r="B6" s="22">
-        <f>Balance!E9</f>
+      <c r="B6" s="28">
+        <f>Balance!E8</f>
         <v/>
       </c>
     </row>
@@ -13844,52 +17252,52 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="16">
-        <f>Balance!A10</f>
+      <c r="A1" s="22">
+        <f>Balance!A9</f>
         <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="17" t="inlineStr">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t>Purse (Cr)</t>
         </is>
       </c>
-      <c r="B3" s="18">
-        <f>Balance!B10</f>
+      <c r="B3" s="24">
+        <f>Balance!B9</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="23" t="inlineStr">
         <is>
           <t>Spent (Cr)</t>
         </is>
       </c>
-      <c r="B4" s="18">
-        <f>Balance!C10</f>
+      <c r="B4" s="24">
+        <f>Balance!C9</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Balance (Cr)</t>
         </is>
       </c>
-      <c r="B5" s="20">
-        <f>Balance!D10</f>
+      <c r="B5" s="26">
+        <f>Balance!D9</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="27" t="inlineStr">
         <is>
           <t>Players</t>
         </is>
       </c>
-      <c r="B6" s="22">
-        <f>Balance!E10</f>
+      <c r="B6" s="28">
+        <f>Balance!E9</f>
         <v/>
       </c>
     </row>
